--- a/Final Expenses 2022 to 2026.xlsx
+++ b/Final Expenses 2022 to 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\payaljaiswani\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24BD4C34-82F8-454D-9CC2-B5561941A6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940ED58D-BFEE-4D6E-9A5E-7AC6D0B88300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A79F9D68-126C-495F-A9F3-01994364D446}"/>
   </bookViews>
@@ -3800,7 +3800,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3963,7 +3963,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4009,14 +4008,6 @@
     <xf numFmtId="14" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4039,27 +4030,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4132,23 +4102,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="2" applyFont="1"/>
@@ -4167,22 +4127,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4203,15 +4157,33 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4620,16 +4592,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="80" t="s">
         <v>1006</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="80" t="s">
         <v>1008</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="80" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -4764,13 +4736,13 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="133" customFormat="1">
-      <c r="A18" s="133" t="s">
+    <row r="18" spans="1:3" s="145" customFormat="1">
+      <c r="A18" s="145" t="s">
         <v>1055</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="80" t="s">
         <v>1028</v>
       </c>
     </row>
@@ -4791,10 +4763,10 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="75" t="s">
         <v>1034</v>
       </c>
-      <c r="B23" s="76" t="s">
+      <c r="B23" s="75" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -4807,10 +4779,10 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="76" t="s">
+      <c r="A25" s="75" t="s">
         <v>1041</v>
       </c>
-      <c r="B25" s="76" t="s">
+      <c r="B25" s="75" t="s">
         <v>1042</v>
       </c>
     </row>
@@ -4846,35 +4818,35 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="141" customFormat="1">
-      <c r="A31" s="141" t="s">
+    <row r="31" spans="1:3" s="125" customFormat="1">
+      <c r="A31" s="125" t="s">
         <v>1049</v>
       </c>
-      <c r="B31" s="141" t="s">
+      <c r="B31" s="125" t="s">
         <v>1050</v>
       </c>
-      <c r="C31" s="141" t="s">
+      <c r="C31" s="125" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="141" customFormat="1">
-      <c r="A32" s="141" t="s">
+    <row r="32" spans="1:3" s="125" customFormat="1">
+      <c r="A32" s="125" t="s">
         <v>1051</v>
       </c>
-      <c r="B32" s="141" t="s">
+      <c r="B32" s="125" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="141" customFormat="1">
-      <c r="A33" s="141" t="s">
+    <row r="33" spans="1:2" s="125" customFormat="1">
+      <c r="A33" s="125" t="s">
         <v>1054</v>
       </c>
-      <c r="B33" s="142" t="s">
+      <c r="B33" s="126" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="140" customFormat="1">
-      <c r="A35" s="140" t="s">
+    <row r="35" spans="1:2" s="124" customFormat="1">
+      <c r="A35" s="124" t="s">
         <v>1059</v>
       </c>
     </row>
@@ -4915,7 +4887,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="76">
+      <c r="A2" s="75">
         <v>44805</v>
       </c>
       <c r="B2" s="2">
@@ -4926,383 +4898,383 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="76">
+      <c r="A3" s="75">
         <v>44835</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="76">
+      <c r="A4" s="75">
         <v>44866</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="76">
+      <c r="A5" s="75">
         <v>44896</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="76">
+      <c r="A6" s="75">
         <v>44927</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="76">
+      <c r="A7" s="75">
         <v>44958</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="76">
+      <c r="A8" s="75">
         <v>44986</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="76">
+      <c r="A9" s="75">
         <v>45017</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="76">
+      <c r="A10" s="75">
         <v>45047</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="76">
+      <c r="A11" s="75">
         <v>45078</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="76">
+      <c r="A12" s="75">
         <v>45108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="76">
+      <c r="A13" s="75">
         <v>45139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="76">
+      <c r="A14" s="75">
         <v>45170</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="76">
+      <c r="A15" s="75">
         <v>45200</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="76">
+      <c r="A16" s="75">
         <v>45231</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="76">
+      <c r="A17" s="75">
         <v>45261</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="76">
+      <c r="A18" s="75">
         <v>45292</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="76">
+      <c r="A19" s="75">
         <v>45323</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="76">
+      <c r="A20" s="75">
         <v>45352</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="76">
+      <c r="A21" s="75">
         <v>45383</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="76">
+      <c r="A22" s="75">
         <v>45413</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="76">
+      <c r="A23" s="75">
         <v>45444</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="76">
+      <c r="A24" s="75">
         <v>45474</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="76">
+      <c r="A25" s="75">
         <v>45505</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="76">
+      <c r="A26" s="75">
         <v>45536</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="76">
+      <c r="A27" s="75">
         <v>45566</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="76">
+      <c r="A28" s="75">
         <v>45597</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="76">
+      <c r="A29" s="75">
         <v>45627</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="76">
+      <c r="A30" s="75">
         <v>45658</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="76">
+      <c r="A31" s="75">
         <v>45689</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="76">
+      <c r="A32" s="75">
         <v>45717</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="76">
+      <c r="A33" s="75">
         <v>45748</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="76">
+      <c r="A34" s="75">
         <v>45778</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="76">
+      <c r="A35" s="75">
         <v>45809</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="76">
+      <c r="A36" s="75">
         <v>45839</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="76">
+      <c r="A37" s="75">
         <v>45870</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="76">
+      <c r="A38" s="75">
         <v>45901</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="76">
+      <c r="A39" s="75">
         <v>45931</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="76">
+      <c r="A40" s="75">
         <v>45962</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="76">
+      <c r="A41" s="75">
         <v>45992</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="76">
+      <c r="A42" s="75">
         <v>46023</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="76">
+      <c r="A43" s="75">
         <v>46054</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="76">
+      <c r="A44" s="75">
         <v>46082</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="76">
+      <c r="A45" s="75">
         <v>46113</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="76">
+      <c r="A46" s="75">
         <v>46143</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="76">
+      <c r="A47" s="75">
         <v>46174</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="76">
+      <c r="A48" s="75">
         <v>46204</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="76">
+      <c r="A49" s="75">
         <v>46235</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="76"/>
+      <c r="A50" s="75"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="76"/>
+      <c r="A51" s="75"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="76"/>
+      <c r="A52" s="75"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="76"/>
+      <c r="A53" s="75"/>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="76"/>
+      <c r="A54" s="75"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="76"/>
+      <c r="A55" s="75"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="76"/>
+      <c r="A56" s="75"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="76"/>
+      <c r="A57" s="75"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="76"/>
+      <c r="A58" s="75"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="76"/>
+      <c r="A59" s="75"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="76"/>
+      <c r="A60" s="75"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="76"/>
+      <c r="A61" s="75"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="76"/>
+      <c r="A62" s="75"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="76"/>
+      <c r="A63" s="75"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="76"/>
+      <c r="A64" s="75"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="76"/>
+      <c r="A65" s="75"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="76"/>
+      <c r="A66" s="75"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="76"/>
+      <c r="A67" s="75"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="76"/>
+      <c r="A68" s="75"/>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="76"/>
+      <c r="A69" s="75"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="76"/>
+      <c r="A70" s="75"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="76"/>
+      <c r="A71" s="75"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="76"/>
+      <c r="A72" s="75"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="76"/>
+      <c r="A73" s="75"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="76"/>
+      <c r="A74" s="75"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="76"/>
+      <c r="A75" s="75"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="76"/>
+      <c r="A76" s="75"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="76"/>
+      <c r="A77" s="75"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="76"/>
+      <c r="A78" s="75"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="76"/>
+      <c r="A79" s="75"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="76"/>
+      <c r="A80" s="75"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="76"/>
+      <c r="A81" s="75"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="76"/>
+      <c r="A82" s="75"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="76"/>
+      <c r="A83" s="75"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="76"/>
+      <c r="A84" s="75"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="76"/>
+      <c r="A85" s="75"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="76"/>
+      <c r="A86" s="75"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="76"/>
+      <c r="A87" s="75"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="76"/>
+      <c r="A88" s="75"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="76"/>
+      <c r="A89" s="75"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="76"/>
+      <c r="A90" s="75"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="76"/>
+      <c r="A91" s="75"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="76"/>
+      <c r="A92" s="75"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="76"/>
+      <c r="A93" s="75"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="76"/>
+      <c r="A94" s="75"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="76"/>
+      <c r="A95" s="75"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="76"/>
+      <c r="A96" s="75"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="76"/>
+      <c r="A97" s="75"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5331,7 +5303,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" s="24" customFormat="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="83" t="s">
         <v>712</v>
       </c>
       <c r="B3" s="24" t="s">
@@ -5371,7 +5343,7 @@
       <c r="A9" s="67" t="s">
         <v>920</v>
       </c>
-      <c r="B9" s="83">
+      <c r="B9" s="82">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -5382,7 +5354,7 @@
       <c r="A10" s="67" t="s">
         <v>921</v>
       </c>
-      <c r="B10" s="83">
+      <c r="B10" s="82">
         <v>1</v>
       </c>
       <c r="C10" t="s">
@@ -5412,7 +5384,7 @@
       <c r="A13" t="s">
         <v>730</v>
       </c>
-      <c r="B13" s="83">
+      <c r="B13" s="82">
         <v>2</v>
       </c>
       <c r="C13" t="s">
@@ -5423,7 +5395,7 @@
       <c r="A14" t="s">
         <v>731</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="82">
         <v>1</v>
       </c>
     </row>
@@ -5431,7 +5403,7 @@
       <c r="A15" t="s">
         <v>732</v>
       </c>
-      <c r="B15" s="83">
+      <c r="B15" s="82">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -5442,7 +5414,7 @@
       <c r="A16" t="s">
         <v>733</v>
       </c>
-      <c r="B16" s="83">
+      <c r="B16" s="82">
         <v>1</v>
       </c>
       <c r="C16" s="67" t="s">
@@ -5453,7 +5425,7 @@
       <c r="A17" t="s">
         <v>735</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="82">
         <v>1</v>
       </c>
       <c r="C17" s="67" t="s">
@@ -5464,7 +5436,7 @@
       <c r="A18" t="s">
         <v>736</v>
       </c>
-      <c r="B18" s="83">
+      <c r="B18" s="82">
         <v>1</v>
       </c>
       <c r="C18" s="67" t="s">
@@ -5475,7 +5447,7 @@
       <c r="A19" t="s">
         <v>739</v>
       </c>
-      <c r="B19" s="83">
+      <c r="B19" s="82">
         <v>1</v>
       </c>
       <c r="C19" s="67" t="s">
@@ -5536,11 +5508,11 @@
     <row r="27" spans="1:3">
       <c r="B27" s="5"/>
     </row>
-    <row r="28" spans="1:3" s="81" customFormat="1">
-      <c r="A28" s="81" t="s">
+    <row r="28" spans="1:3" s="80" customFormat="1">
+      <c r="A28" s="80" t="s">
         <v>916</v>
       </c>
-      <c r="B28" s="82"/>
+      <c r="B28" s="81"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
@@ -5848,7 +5820,7 @@
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="140" t="s">
+      <c r="A73" s="124" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -6143,7 +6115,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="52" customFormat="1">
-      <c r="A11" s="87">
+      <c r="A11" s="86">
         <v>44834</v>
       </c>
       <c r="B11" s="51">
@@ -6530,8 +6502,8 @@
         <v>526</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="68" customFormat="1" ht="18.5">
-      <c r="A28" s="68" t="s">
+    <row r="28" spans="1:9" s="144" customFormat="1" ht="18.5">
+      <c r="A28" s="144" t="s">
         <v>663</v>
       </c>
     </row>
@@ -6549,7 +6521,7 @@
       <c r="C30" s="31">
         <v>4200</v>
       </c>
-      <c r="D30" s="85" t="s">
+      <c r="D30" s="84" t="s">
         <v>160</v>
       </c>
       <c r="E30" s="31" t="s">
@@ -6700,7 +6672,7 @@
       <c r="F35" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="85" t="s">
+      <c r="G35" s="84" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="31" t="s">
@@ -6754,7 +6726,7 @@
       <c r="F37" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="G37" s="85" t="s">
+      <c r="G37" s="84" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="31" t="s">
@@ -6815,28 +6787,28 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="156" customFormat="1">
-      <c r="A40" s="154">
+    <row r="40" spans="1:10" s="138" customFormat="1">
+      <c r="A40" s="136">
         <v>45287</v>
       </c>
-      <c r="B40" s="155">
+      <c r="B40" s="137">
         <v>361.2</v>
       </c>
-      <c r="C40" s="155">
+      <c r="C40" s="137">
         <v>30000</v>
       </c>
-      <c r="D40" s="156" t="s">
+      <c r="D40" s="138" t="s">
         <v>167</v>
       </c>
-      <c r="E40" s="155" t="s">
+      <c r="E40" s="137" t="s">
         <v>118</v>
       </c>
-      <c r="F40" s="155"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="155" t="s">
+      <c r="F40" s="137"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="137" t="s">
         <v>1068</v>
       </c>
-      <c r="I40" s="157" t="s">
+      <c r="I40" s="139" t="s">
         <v>167</v>
       </c>
     </row>
@@ -6883,76 +6855,76 @@
       <c r="H42" s="31" t="s">
         <v>1097</v>
       </c>
-      <c r="I42" s="85" t="s">
+      <c r="I42" s="84" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="160" customFormat="1">
-      <c r="A43" s="158">
+    <row r="43" spans="1:10" s="142" customFormat="1">
+      <c r="A43" s="140">
         <v>45305</v>
       </c>
-      <c r="B43" s="159">
+      <c r="B43" s="141">
         <v>301.02</v>
       </c>
-      <c r="C43" s="159">
+      <c r="C43" s="141">
         <v>25000</v>
       </c>
-      <c r="D43" s="160" t="s">
+      <c r="D43" s="142" t="s">
         <v>1066</v>
       </c>
-      <c r="E43" s="159" t="s">
+      <c r="E43" s="141" t="s">
         <v>1104</v>
       </c>
-      <c r="F43" s="159"/>
-      <c r="H43" s="159" t="s">
+      <c r="F43" s="141"/>
+      <c r="H43" s="141" t="s">
         <v>1105</v>
       </c>
-      <c r="I43" s="161" t="s">
+      <c r="I43" s="143" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="160" customFormat="1">
-      <c r="A44" s="158">
+    <row r="44" spans="1:10" s="142" customFormat="1">
+      <c r="A44" s="140">
         <v>45304</v>
       </c>
-      <c r="B44" s="159">
+      <c r="B44" s="141">
         <v>300.83999999999997</v>
       </c>
-      <c r="C44" s="159">
+      <c r="C44" s="141">
         <v>25000</v>
       </c>
-      <c r="D44" s="160" t="s">
+      <c r="D44" s="142" t="s">
         <v>1066</v>
       </c>
-      <c r="E44" s="159" t="s">
+      <c r="E44" s="141" t="s">
         <v>1104</v>
       </c>
-      <c r="F44" s="159"/>
-      <c r="H44" s="159" t="s">
+      <c r="F44" s="141"/>
+      <c r="H44" s="141" t="s">
         <v>1105</v>
       </c>
-      <c r="I44" s="161" t="s">
+      <c r="I44" s="143" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="66" customFormat="1">
-      <c r="A45" s="108">
+      <c r="A45" s="96">
         <v>45657</v>
       </c>
-      <c r="B45" s="109">
+      <c r="B45" s="97">
         <v>58.45</v>
       </c>
-      <c r="C45" s="109">
+      <c r="C45" s="97">
         <v>5000</v>
       </c>
       <c r="D45" s="66" t="s">
         <v>1067</v>
       </c>
-      <c r="E45" s="109" t="s">
+      <c r="E45" s="97" t="s">
         <v>118</v>
       </c>
-      <c r="F45" s="109"/>
-      <c r="H45" s="109" t="s">
+      <c r="F45" s="97"/>
+      <c r="H45" s="97" t="s">
         <v>1091</v>
       </c>
       <c r="I45" s="66" t="s">
@@ -6960,25 +6932,25 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="66" customFormat="1">
-      <c r="A46" s="108">
+      <c r="A46" s="96">
         <v>45657</v>
       </c>
-      <c r="B46" s="109">
+      <c r="B46" s="97">
         <v>467.6</v>
       </c>
-      <c r="C46" s="109">
+      <c r="C46" s="97">
         <v>40000</v>
       </c>
       <c r="D46" s="66" t="s">
         <v>1067</v>
       </c>
-      <c r="E46" s="109" t="s">
+      <c r="E46" s="97" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="109" t="s">
+      <c r="F46" s="97" t="s">
         <v>119</v>
       </c>
-      <c r="H46" s="109" t="s">
+      <c r="H46" s="97" t="s">
         <v>1090</v>
       </c>
       <c r="I46" s="66" t="s">
@@ -6989,50 +6961,50 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="66" customFormat="1">
-      <c r="A47" s="108">
+      <c r="A47" s="96">
         <v>45657</v>
       </c>
-      <c r="B47" s="109">
+      <c r="B47" s="97">
         <v>9.24</v>
       </c>
-      <c r="C47" s="109">
+      <c r="C47" s="97">
         <v>790</v>
       </c>
       <c r="D47" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="E47" s="109" t="s">
+      <c r="E47" s="97" t="s">
         <v>1095</v>
       </c>
-      <c r="F47" s="109"/>
-      <c r="H47" s="109" t="s">
+      <c r="F47" s="97"/>
+      <c r="H47" s="97" t="s">
         <v>1096</v>
       </c>
       <c r="I47" s="66" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="164" customFormat="1">
-      <c r="A48" s="162">
+    <row r="48" spans="1:10" s="66" customFormat="1">
+      <c r="A48" s="96">
         <v>45323</v>
       </c>
-      <c r="B48" s="163">
+      <c r="B48" s="97">
         <v>25.29</v>
       </c>
-      <c r="C48" s="163">
+      <c r="C48" s="97">
         <v>2100</v>
       </c>
-      <c r="D48" s="164" t="s">
+      <c r="D48" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="E48" s="163" t="s">
+      <c r="E48" s="97" t="s">
         <v>1099</v>
       </c>
-      <c r="F48" s="163"/>
-      <c r="H48" s="163" t="s">
+      <c r="F48" s="97"/>
+      <c r="H48" s="97" t="s">
         <v>1100</v>
       </c>
-      <c r="I48" s="164" t="s">
+      <c r="I48" s="66" t="s">
         <v>167</v>
       </c>
     </row>
@@ -7149,77 +7121,77 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="81" customFormat="1">
-      <c r="A53" s="145">
+    <row r="53" spans="1:11" s="80" customFormat="1">
+      <c r="A53" s="129">
         <v>45289</v>
       </c>
-      <c r="B53" s="146">
+      <c r="B53" s="130">
         <v>240.48</v>
       </c>
-      <c r="C53" s="146">
+      <c r="C53" s="130">
         <v>20000</v>
       </c>
-      <c r="D53" s="81" t="s">
+      <c r="D53" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="E53" s="146" t="s">
+      <c r="E53" s="130" t="s">
         <v>1061</v>
       </c>
-      <c r="H53" s="81" t="s">
+      <c r="H53" s="80" t="s">
         <v>1063</v>
       </c>
-      <c r="I53" s="81" t="s">
+      <c r="I53" s="80" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="91" customFormat="1">
-      <c r="A54" s="148">
+    <row r="54" spans="1:11">
+      <c r="A54" s="11">
         <v>45289</v>
       </c>
-      <c r="B54" s="149">
+      <c r="B54" s="2">
         <v>514.16999999999996</v>
       </c>
-      <c r="C54" s="149">
+      <c r="C54" s="2">
         <v>42760</v>
       </c>
-      <c r="D54" s="91" t="s">
+      <c r="D54" t="s">
         <v>160</v>
       </c>
-      <c r="E54" s="149" t="s">
+      <c r="E54" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="149" t="s">
+      <c r="F54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G54" s="165" t="s">
+      <c r="G54" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H54" s="91" t="s">
+      <c r="H54" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="91" customFormat="1">
-      <c r="A55" s="148">
+    <row r="55" spans="1:11">
+      <c r="A55" s="11">
         <v>45290</v>
       </c>
-      <c r="B55" s="149">
+      <c r="B55" s="2">
         <v>16.78</v>
       </c>
-      <c r="C55" s="149">
+      <c r="C55" s="2">
         <v>1395</v>
       </c>
-      <c r="D55" s="91" t="s">
+      <c r="D55" t="s">
         <v>160</v>
       </c>
-      <c r="E55" s="149" t="s">
+      <c r="E55" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="149"/>
-      <c r="G55" s="165"/>
-      <c r="H55" s="91" t="s">
+      <c r="F55" s="2"/>
+      <c r="G55" s="5"/>
+      <c r="H55" t="s">
         <v>1062</v>
       </c>
-      <c r="I55" s="91" t="s">
+      <c r="I55" t="s">
         <v>160</v>
       </c>
     </row>
@@ -7471,32 +7443,32 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:16384" s="90" customFormat="1">
-      <c r="A65" s="88">
+    <row r="65" spans="1:16384" s="7" customFormat="1">
+      <c r="A65" s="42">
         <v>45231</v>
       </c>
-      <c r="B65" s="89">
+      <c r="B65" s="8">
         <v>58.99</v>
       </c>
-      <c r="C65" s="89">
+      <c r="C65" s="8">
         <v>4910</v>
       </c>
-      <c r="D65" s="90" t="s">
+      <c r="D65" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E65" s="89" t="s">
+      <c r="E65" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F65" s="90" t="s">
+      <c r="F65" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G65" s="90" t="s">
+      <c r="G65" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H65" s="90" t="s">
+      <c r="H65" s="7" t="s">
         <v>939</v>
       </c>
-      <c r="I65" s="90" t="s">
+      <c r="I65" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -57021,13 +56993,13 @@
       </c>
     </row>
     <row r="102" spans="1:9" s="66" customFormat="1">
-      <c r="A102" s="108">
+      <c r="A102" s="96">
         <v>45298</v>
       </c>
-      <c r="B102" s="109">
+      <c r="B102" s="97">
         <v>145</v>
       </c>
-      <c r="C102" s="109">
+      <c r="C102" s="97">
         <v>12000</v>
       </c>
       <c r="D102" s="66" t="s">
@@ -57214,32 +57186,32 @@
         <v>135</v>
       </c>
     </row>
-    <row r="110" spans="1:9" s="91" customFormat="1">
-      <c r="A110" s="148">
+    <row r="110" spans="1:9">
+      <c r="A110" s="11">
         <v>45250</v>
       </c>
-      <c r="B110" s="149">
+      <c r="B110" s="2">
         <v>24.6</v>
       </c>
-      <c r="C110" s="149">
+      <c r="C110" s="2">
         <v>2050</v>
       </c>
-      <c r="D110" s="91" t="s">
+      <c r="D110" t="s">
         <v>167</v>
       </c>
-      <c r="E110" s="91" t="s">
+      <c r="E110" t="s">
         <v>544</v>
       </c>
-      <c r="F110" s="91" t="s">
+      <c r="F110" t="s">
         <v>546</v>
       </c>
-      <c r="G110" s="91" t="s">
+      <c r="G110" t="s">
         <v>545</v>
       </c>
-      <c r="H110" s="91" t="s">
+      <c r="H110" t="s">
         <v>548</v>
       </c>
-      <c r="I110" s="91" t="s">
+      <c r="I110" t="s">
         <v>547</v>
       </c>
     </row>
@@ -57443,7 +57415,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" ht="28.5">
       <c r="A118" s="11">
         <v>45291</v>
       </c>
@@ -57844,7 +57816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" ht="28.5">
       <c r="A132" s="11">
         <v>45302</v>
       </c>
@@ -57948,7 +57920,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" ht="28.5">
       <c r="A136" s="11">
         <v>45304</v>
       </c>
@@ -57958,7 +57930,7 @@
       <c r="C136" s="2">
         <v>20000</v>
       </c>
-      <c r="D136" s="92" t="s">
+      <c r="D136" s="87" t="s">
         <v>298</v>
       </c>
       <c r="E136" t="s">
@@ -57977,7 +57949,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" ht="28.5">
       <c r="A137" s="11">
         <v>45305</v>
       </c>
@@ -57987,7 +57959,7 @@
       <c r="C137" s="2">
         <v>2500</v>
       </c>
-      <c r="D137" s="93" t="s">
+      <c r="D137" s="88" t="s">
         <v>299</v>
       </c>
       <c r="E137" t="s">
@@ -58113,7 +58085,7 @@
       <c r="D142" t="s">
         <v>52</v>
       </c>
-      <c r="E142" s="91" t="s">
+      <c r="E142" t="s">
         <v>683</v>
       </c>
       <c r="G142" t="s">
@@ -58189,24 +58161,24 @@
         <v>554</v>
       </c>
     </row>
-    <row r="146" spans="1:9" s="153" customFormat="1">
-      <c r="A146" s="150">
+    <row r="146" spans="1:9" s="135" customFormat="1">
+      <c r="A146" s="132">
         <v>45300</v>
       </c>
-      <c r="B146" s="151"/>
-      <c r="C146" s="151">
+      <c r="B146" s="133"/>
+      <c r="C146" s="133">
         <v>7100</v>
       </c>
-      <c r="D146" s="152" t="s">
+      <c r="D146" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="E146" s="153" t="s">
+      <c r="E146" s="135" t="s">
         <v>961</v>
       </c>
-      <c r="H146" s="153" t="s">
+      <c r="H146" s="135" t="s">
         <v>779</v>
       </c>
-      <c r="I146" s="153" t="s">
+      <c r="I146" s="135" t="s">
         <v>150</v>
       </c>
     </row>
@@ -58415,26 +58387,26 @@
         <v>254</v>
       </c>
     </row>
-    <row r="159" spans="1:9" s="160" customFormat="1">
-      <c r="A159" s="158">
+    <row r="159" spans="1:9" s="142" customFormat="1">
+      <c r="A159" s="140">
         <v>45303</v>
       </c>
-      <c r="B159" s="159">
+      <c r="B159" s="141">
         <v>187.78</v>
       </c>
-      <c r="C159" s="159">
+      <c r="C159" s="141">
         <v>15600</v>
       </c>
-      <c r="D159" s="160" t="s">
+      <c r="D159" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="E159" s="160" t="s">
+      <c r="E159" s="142" t="s">
         <v>710</v>
       </c>
-      <c r="H159" s="160" t="s">
+      <c r="H159" s="142" t="s">
         <v>1109</v>
       </c>
-      <c r="I159" s="160" t="s">
+      <c r="I159" s="142" t="s">
         <v>150</v>
       </c>
     </row>
@@ -58660,6 +58632,9 @@
       <c r="A170" s="11">
         <v>45201</v>
       </c>
+      <c r="B170" s="2">
+        <v>185.38</v>
+      </c>
       <c r="C170" s="2">
         <v>15418</v>
       </c>
@@ -58684,23 +58659,23 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="176" spans="1:9" s="135" customFormat="1" ht="16">
-      <c r="A176" s="135" t="s">
+    <row r="176" spans="1:9" s="121" customFormat="1" ht="16">
+      <c r="A176" s="121" t="s">
         <v>1000</v>
       </c>
-      <c r="B176" s="136"/>
+      <c r="B176" s="122"/>
     </row>
     <row r="178" spans="1:7" s="64" customFormat="1">
       <c r="A178" s="64" t="s">
         <v>1001</v>
       </c>
-      <c r="B178" s="98"/>
+      <c r="B178" s="93"/>
     </row>
     <row r="180" spans="1:7" s="64" customFormat="1">
       <c r="A180" s="64" t="s">
         <v>1002</v>
       </c>
-      <c r="B180" s="98"/>
+      <c r="B180" s="93"/>
     </row>
     <row r="181" spans="1:7" s="44" customFormat="1">
       <c r="A181" s="47"/>
@@ -58709,14 +58684,14 @@
       <c r="F181" s="45"/>
       <c r="G181" s="45"/>
     </row>
-    <row r="182" spans="1:7" s="139" customFormat="1">
+    <row r="182" spans="1:7" s="3" customFormat="1">
       <c r="A182" s="64" t="s">
         <v>1003</v>
       </c>
-      <c r="B182" s="137"/>
-      <c r="C182" s="138"/>
-      <c r="F182" s="137"/>
-      <c r="G182" s="137"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="123"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="4"/>
     </row>
     <row r="183" spans="1:7" s="44" customFormat="1">
       <c r="A183" s="47"/>
@@ -59046,26 +59021,26 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="95">
+      <c r="A10" s="90">
         <v>45073</v>
       </c>
-      <c r="B10" s="96">
+      <c r="B10" s="91">
         <v>1</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="91" t="s">
         <v>991</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="E10" s="91" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="G10" s="97">
+      <c r="G10" s="92">
         <v>1845</v>
       </c>
-      <c r="H10" s="97">
+      <c r="H10" s="92">
         <v>152348</v>
       </c>
       <c r="I10" t="s">
@@ -59179,11 +59154,11 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.5">
+    <row r="15" spans="1:9" ht="42.5">
       <c r="A15" s="12">
         <v>45233</v>
       </c>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="88" t="s">
         <v>686</v>
       </c>
       <c r="C15" t="s">
@@ -59208,11 +59183,11 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="28.5">
+    <row r="16" spans="1:9" ht="42.5">
       <c r="A16" s="11">
         <v>45254</v>
       </c>
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="88" t="s">
         <v>688</v>
       </c>
       <c r="C16" t="s">
@@ -59301,7 +59276,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="66" customFormat="1">
-      <c r="A20" s="108">
+      <c r="A20" s="96">
         <v>44039</v>
       </c>
       <c r="C20" s="66" t="s">
@@ -59316,10 +59291,10 @@
       <c r="F20" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="G20" s="109">
+      <c r="G20" s="97">
         <v>1190.7</v>
       </c>
-      <c r="H20" s="109" t="s">
+      <c r="H20" s="97" t="s">
         <v>984</v>
       </c>
     </row>
@@ -59377,7 +59352,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="66" customFormat="1">
-      <c r="A24" s="109" t="s">
+      <c r="A24" s="97" t="s">
         <v>977</v>
       </c>
       <c r="B24" s="66">
@@ -59395,15 +59370,15 @@
       <c r="F24" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="G24" s="109" t="s">
+      <c r="G24" s="97" t="s">
         <v>979</v>
       </c>
-      <c r="H24" s="109" t="s">
+      <c r="H24" s="97" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="94">
+      <c r="A25" s="89">
         <v>45134</v>
       </c>
       <c r="B25" s="6"/>
@@ -59432,28 +59407,28 @@
     <row r="27" spans="1:9">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:9" s="103" customFormat="1">
-      <c r="A28" s="102" t="s">
+    <row r="28" spans="1:9" s="147" customFormat="1">
+      <c r="A28" s="146" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="105" customFormat="1">
-      <c r="A29" s="104"/>
-    </row>
-    <row r="30" spans="1:9" s="105" customFormat="1">
-      <c r="A30" s="104"/>
-    </row>
-    <row r="31" spans="1:9" s="105" customFormat="1">
-      <c r="A31" s="104"/>
-    </row>
-    <row r="32" spans="1:9" s="105" customFormat="1">
-      <c r="A32" s="104"/>
-    </row>
-    <row r="33" spans="1:1" s="105" customFormat="1">
-      <c r="A33" s="104"/>
-    </row>
-    <row r="34" spans="1:1" s="107" customFormat="1">
-      <c r="A34" s="106"/>
+    <row r="29" spans="1:9" s="149" customFormat="1">
+      <c r="A29" s="148"/>
+    </row>
+    <row r="30" spans="1:9" s="149" customFormat="1">
+      <c r="A30" s="148"/>
+    </row>
+    <row r="31" spans="1:9" s="149" customFormat="1">
+      <c r="A31" s="148"/>
+    </row>
+    <row r="32" spans="1:9" s="149" customFormat="1">
+      <c r="A32" s="148"/>
+    </row>
+    <row r="33" spans="1:1" s="149" customFormat="1">
+      <c r="A33" s="148"/>
+    </row>
+    <row r="34" spans="1:1" s="151" customFormat="1">
+      <c r="A34" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -59477,2385 +59452,2385 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="68" t="s">
         <v>225</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E1" s="69" t="s">
         <v>790</v>
       </c>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="69" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="86" customFormat="1">
-      <c r="A2" s="110">
+    <row r="2" spans="1:6" s="85" customFormat="1">
+      <c r="A2" s="98">
         <v>44812</v>
       </c>
-      <c r="B2" s="111">
+      <c r="B2" s="99">
         <v>18.809999999999999</v>
       </c>
-      <c r="C2" s="112">
+      <c r="C2" s="100">
         <v>1499</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="E2" s="101" t="s">
         <v>538</v>
       </c>
-      <c r="F2" s="113" t="s">
+      <c r="F2" s="101" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="86" customFormat="1">
-      <c r="A3" s="110">
+    <row r="3" spans="1:6" s="85" customFormat="1">
+      <c r="A3" s="98">
         <v>44813</v>
       </c>
-      <c r="B3" s="111">
+      <c r="B3" s="99">
         <v>6.33</v>
       </c>
-      <c r="C3" s="112">
+      <c r="C3" s="100">
         <v>504</v>
       </c>
-      <c r="D3" s="113" t="s">
+      <c r="D3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="E3" s="101" t="s">
         <v>793</v>
       </c>
-      <c r="F3" s="113" t="s">
+      <c r="F3" s="101" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="86" customFormat="1">
-      <c r="A4" s="110">
+    <row r="4" spans="1:6" s="85" customFormat="1">
+      <c r="A4" s="98">
         <v>44844</v>
       </c>
-      <c r="B4" s="111">
+      <c r="B4" s="99">
         <v>32.15</v>
       </c>
-      <c r="C4" s="112">
+      <c r="C4" s="100">
         <v>2650</v>
       </c>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="113" t="s">
+      <c r="E4" s="101" t="s">
         <v>794</v>
       </c>
-      <c r="F4" s="113" t="s">
+      <c r="F4" s="101" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="86" customFormat="1">
-      <c r="A5" s="110">
+    <row r="5" spans="1:6" s="85" customFormat="1">
+      <c r="A5" s="98">
         <v>44844</v>
       </c>
-      <c r="B5" s="111">
+      <c r="B5" s="99">
         <v>8.9700000000000006</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="100">
         <v>739</v>
       </c>
-      <c r="D5" s="113" t="s">
+      <c r="D5" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="113" t="s">
+      <c r="E5" s="101" t="s">
         <v>796</v>
       </c>
-      <c r="F5" s="113" t="s">
+      <c r="F5" s="101" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="86" customFormat="1">
-      <c r="A6" s="110">
+    <row r="6" spans="1:6" s="85" customFormat="1">
+      <c r="A6" s="98">
         <v>44895</v>
       </c>
-      <c r="B6" s="111">
+      <c r="B6" s="99">
         <v>32.26</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="100">
         <v>2631</v>
       </c>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="113" t="s">
+      <c r="E6" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="113" t="s">
+      <c r="F6" s="101" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="86" customFormat="1">
-      <c r="A7" s="110">
+    <row r="7" spans="1:6" s="85" customFormat="1">
+      <c r="A7" s="98">
         <v>44895</v>
       </c>
-      <c r="B7" s="111">
+      <c r="B7" s="99">
         <v>11.19</v>
       </c>
-      <c r="C7" s="112">
+      <c r="C7" s="100">
         <v>908</v>
       </c>
-      <c r="D7" s="113" t="s">
+      <c r="D7" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="113" t="s">
+      <c r="E7" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="113" t="s">
+      <c r="F7" s="101" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="86" customFormat="1">
-      <c r="A8" s="110">
+    <row r="8" spans="1:6" s="85" customFormat="1">
+      <c r="A8" s="98">
         <v>44896</v>
       </c>
-      <c r="B8" s="111">
+      <c r="B8" s="99">
         <v>9.49</v>
       </c>
-      <c r="C8" s="112">
+      <c r="C8" s="100">
         <v>773</v>
       </c>
-      <c r="D8" s="113" t="s">
+      <c r="D8" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="113" t="s">
+      <c r="E8" s="101" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="113" t="s">
+      <c r="F8" s="101" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="86" customFormat="1">
-      <c r="A9" s="110">
+    <row r="9" spans="1:6" s="85" customFormat="1">
+      <c r="A9" s="98">
         <v>44889</v>
       </c>
-      <c r="B9" s="111">
+      <c r="B9" s="99">
         <v>43.75</v>
       </c>
-      <c r="C9" s="112">
+      <c r="C9" s="100">
         <v>3573</v>
       </c>
-      <c r="D9" s="113" t="s">
+      <c r="D9" s="101" t="s">
         <v>798</v>
       </c>
-      <c r="E9" s="113" t="s">
+      <c r="E9" s="101" t="s">
         <v>799</v>
       </c>
-      <c r="F9" s="113" t="s">
+      <c r="F9" s="101" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="99" customFormat="1">
-      <c r="A10" s="114">
+    <row r="10" spans="1:6" s="94" customFormat="1">
+      <c r="A10" s="102">
         <v>44994</v>
       </c>
-      <c r="B10" s="115">
+      <c r="B10" s="103">
         <v>4.88</v>
       </c>
-      <c r="C10" s="116">
+      <c r="C10" s="104">
         <v>400</v>
       </c>
-      <c r="D10" s="117" t="s">
+      <c r="D10" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="117" t="s">
+      <c r="E10" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="117" t="s">
+      <c r="F10" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="99" customFormat="1">
-      <c r="A11" s="114">
+    <row r="11" spans="1:6" s="94" customFormat="1">
+      <c r="A11" s="102">
         <v>44994</v>
       </c>
-      <c r="B11" s="115">
+      <c r="B11" s="103">
         <v>28.06</v>
       </c>
-      <c r="C11" s="116">
+      <c r="C11" s="104">
         <v>2300</v>
       </c>
-      <c r="D11" s="117" t="s">
+      <c r="D11" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="117" t="s">
+      <c r="E11" s="105" t="s">
         <v>541</v>
       </c>
-      <c r="F11" s="117" t="s">
+      <c r="F11" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="99" customFormat="1">
-      <c r="A12" s="114">
+    <row r="12" spans="1:6" s="94" customFormat="1">
+      <c r="A12" s="102">
         <v>44994</v>
       </c>
-      <c r="B12" s="115">
+      <c r="B12" s="103">
         <v>5.12</v>
       </c>
-      <c r="C12" s="116">
+      <c r="C12" s="104">
         <v>420</v>
       </c>
-      <c r="D12" s="117" t="s">
+      <c r="D12" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="117" t="s">
+      <c r="E12" s="105" t="s">
         <v>801</v>
       </c>
-      <c r="F12" s="117" t="s">
+      <c r="F12" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="99" customFormat="1">
-      <c r="A13" s="114">
+    <row r="13" spans="1:6" s="94" customFormat="1">
+      <c r="A13" s="102">
         <v>44996</v>
       </c>
-      <c r="B13" s="115">
+      <c r="B13" s="103">
         <v>11.92</v>
       </c>
-      <c r="C13" s="116">
+      <c r="C13" s="104">
         <v>980.11</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="105" t="s">
         <v>893</v>
       </c>
-      <c r="E13" s="117" t="s">
+      <c r="E13" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="117" t="s">
+      <c r="F13" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="99" customFormat="1">
-      <c r="A14" s="114">
+    <row r="14" spans="1:6" s="94" customFormat="1">
+      <c r="A14" s="102">
         <v>44996</v>
       </c>
-      <c r="B14" s="115">
+      <c r="B14" s="103">
         <v>9.4700000000000006</v>
       </c>
-      <c r="C14" s="116">
+      <c r="C14" s="104">
         <v>779.17</v>
       </c>
-      <c r="D14" s="117" t="s">
+      <c r="D14" s="105" t="s">
         <v>893</v>
       </c>
-      <c r="E14" s="117" t="s">
+      <c r="E14" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="117" t="s">
+      <c r="F14" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="99" customFormat="1">
-      <c r="A15" s="114">
+    <row r="15" spans="1:6" s="94" customFormat="1">
+      <c r="A15" s="102">
         <v>44996</v>
       </c>
-      <c r="B15" s="115">
+      <c r="B15" s="103">
         <v>122.97</v>
       </c>
-      <c r="C15" s="116">
+      <c r="C15" s="104">
         <v>10080</v>
       </c>
-      <c r="D15" s="117" t="s">
+      <c r="D15" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="105" t="s">
         <v>802</v>
       </c>
-      <c r="F15" s="117" t="s">
+      <c r="F15" s="105" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="99" customFormat="1">
-      <c r="A16" s="114">
+    <row r="16" spans="1:6" s="94" customFormat="1">
+      <c r="A16" s="102">
         <v>44996</v>
       </c>
-      <c r="B16" s="115">
+      <c r="B16" s="103">
         <v>51.68</v>
       </c>
-      <c r="C16" s="116">
+      <c r="C16" s="104">
         <v>4236</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="117" t="s">
+      <c r="E16" s="105" t="s">
         <v>802</v>
       </c>
-      <c r="F16" s="117" t="s">
+      <c r="F16" s="105" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="99" customFormat="1">
-      <c r="A17" s="114">
+    <row r="17" spans="1:6" s="94" customFormat="1">
+      <c r="A17" s="102">
         <v>44999</v>
       </c>
-      <c r="B17" s="115">
+      <c r="B17" s="103">
         <v>25.01</v>
       </c>
-      <c r="C17" s="116">
+      <c r="C17" s="104">
         <v>2050</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="117" t="s">
+      <c r="E17" s="105" t="s">
         <v>804</v>
       </c>
-      <c r="F17" s="117" t="s">
+      <c r="F17" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="99" customFormat="1">
-      <c r="A18" s="114">
+    <row r="18" spans="1:6" s="94" customFormat="1">
+      <c r="A18" s="102">
         <v>44999</v>
       </c>
-      <c r="B18" s="115">
+      <c r="B18" s="103">
         <v>111.62</v>
       </c>
-      <c r="C18" s="116">
+      <c r="C18" s="104">
         <v>9150</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="105" t="s">
         <v>542</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="105" t="s">
         <v>542</v>
       </c>
-      <c r="F18" s="117" t="s">
+      <c r="F18" s="105" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="99" customFormat="1">
-      <c r="A19" s="114">
+    <row r="19" spans="1:6" s="94" customFormat="1">
+      <c r="A19" s="102">
         <v>44999</v>
       </c>
-      <c r="B19" s="115">
+      <c r="B19" s="103">
         <v>65.069999999999993</v>
       </c>
-      <c r="C19" s="116">
+      <c r="C19" s="104">
         <v>5334</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="117" t="s">
+      <c r="E19" s="105" t="s">
         <v>605</v>
       </c>
-      <c r="F19" s="117" t="s">
+      <c r="F19" s="105" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="99" customFormat="1">
-      <c r="A20" s="114">
+    <row r="20" spans="1:6" s="94" customFormat="1">
+      <c r="A20" s="102">
         <v>45000</v>
       </c>
-      <c r="B20" s="115">
+      <c r="B20" s="103">
         <v>48.46</v>
       </c>
-      <c r="C20" s="116">
+      <c r="C20" s="104">
         <v>4000</v>
       </c>
-      <c r="D20" s="117" t="s">
+      <c r="D20" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="117" t="s">
+      <c r="E20" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="117" t="s">
+      <c r="F20" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="99" customFormat="1">
-      <c r="A21" s="114">
+    <row r="21" spans="1:6" s="94" customFormat="1">
+      <c r="A21" s="102">
         <v>45000</v>
       </c>
-      <c r="B21" s="115">
+      <c r="B21" s="103">
         <v>15.69</v>
       </c>
-      <c r="C21" s="116">
+      <c r="C21" s="104">
         <v>1500</v>
       </c>
-      <c r="D21" s="117" t="s">
+      <c r="D21" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="117" t="s">
+      <c r="E21" s="105" t="s">
         <v>806</v>
       </c>
-      <c r="F21" s="117" t="s">
+      <c r="F21" s="105" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="99" customFormat="1">
-      <c r="A22" s="114">
+    <row r="22" spans="1:6" s="94" customFormat="1">
+      <c r="A22" s="102">
         <v>45000</v>
       </c>
-      <c r="B22" s="115">
+      <c r="B22" s="103">
         <v>3.02</v>
       </c>
-      <c r="C22" s="116">
+      <c r="C22" s="104">
         <v>220</v>
       </c>
-      <c r="D22" s="117" t="s">
+      <c r="D22" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E22" s="117" t="s">
+      <c r="E22" s="105" t="s">
         <v>808</v>
       </c>
-      <c r="F22" s="117" t="s">
+      <c r="F22" s="105" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="99" customFormat="1">
-      <c r="A23" s="114">
+    <row r="23" spans="1:6" s="94" customFormat="1">
+      <c r="A23" s="102">
         <v>45000</v>
       </c>
-      <c r="B23" s="115">
+      <c r="B23" s="103">
         <v>2.66</v>
       </c>
-      <c r="C23" s="116">
+      <c r="C23" s="104">
         <v>250</v>
       </c>
-      <c r="D23" s="117" t="s">
+      <c r="D23" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E23" s="117" t="s">
+      <c r="E23" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="F23" s="117" t="s">
+      <c r="F23" s="105" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="99" customFormat="1" ht="29">
-      <c r="A24" s="114">
+    <row r="24" spans="1:6" s="94" customFormat="1" ht="29">
+      <c r="A24" s="102">
         <v>45000</v>
       </c>
-      <c r="B24" s="115">
+      <c r="B24" s="103">
         <v>67.62</v>
       </c>
-      <c r="C24" s="116" t="s">
+      <c r="C24" s="104" t="s">
         <v>787</v>
       </c>
-      <c r="D24" s="117" t="s">
+      <c r="D24" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="117" t="s">
+      <c r="E24" s="105" t="s">
         <v>811</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F24" s="105" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="99" customFormat="1">
-      <c r="A25" s="114">
+    <row r="25" spans="1:6" s="94" customFormat="1">
+      <c r="A25" s="102">
         <v>45000</v>
       </c>
-      <c r="B25" s="115">
+      <c r="B25" s="103">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C25" s="116">
+      <c r="C25" s="104">
         <v>90</v>
       </c>
-      <c r="D25" s="117" t="s">
+      <c r="D25" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="117" t="s">
+      <c r="E25" s="105" t="s">
         <v>813</v>
       </c>
-      <c r="F25" s="117" t="s">
+      <c r="F25" s="105" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="99" customFormat="1">
-      <c r="A26" s="114">
+    <row r="26" spans="1:6" s="94" customFormat="1">
+      <c r="A26" s="102">
         <v>45000</v>
       </c>
-      <c r="B26" s="115">
+      <c r="B26" s="103">
         <v>3.63</v>
       </c>
-      <c r="C26" s="116">
+      <c r="C26" s="104">
         <v>300</v>
       </c>
-      <c r="D26" s="117" t="s">
+      <c r="D26" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="117" t="s">
+      <c r="E26" s="105" t="s">
         <v>814</v>
       </c>
-      <c r="F26" s="117" t="s">
+      <c r="F26" s="105" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="99" customFormat="1">
-      <c r="A27" s="114">
+    <row r="27" spans="1:6" s="94" customFormat="1">
+      <c r="A27" s="102">
         <v>45000</v>
       </c>
-      <c r="B27" s="115">
+      <c r="B27" s="103">
         <v>12.1</v>
       </c>
-      <c r="C27" s="116">
+      <c r="C27" s="104">
         <v>1000</v>
       </c>
-      <c r="D27" s="117" t="s">
+      <c r="D27" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E27" s="117" t="s">
+      <c r="E27" s="105" t="s">
         <v>815</v>
       </c>
-      <c r="F27" s="117" t="s">
+      <c r="F27" s="105" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="99" customFormat="1">
-      <c r="A28" s="114">
+    <row r="28" spans="1:6" s="94" customFormat="1">
+      <c r="A28" s="102">
         <v>45000</v>
       </c>
-      <c r="B28" s="115">
+      <c r="B28" s="103">
         <v>11.57</v>
       </c>
-      <c r="C28" s="116">
+      <c r="C28" s="104">
         <v>956</v>
       </c>
-      <c r="D28" s="117" t="s">
+      <c r="D28" s="105" t="s">
         <v>893</v>
       </c>
-      <c r="E28" s="117" t="s">
+      <c r="E28" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="117" t="s">
+      <c r="F28" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="99" customFormat="1">
-      <c r="A29" s="114">
+    <row r="29" spans="1:6" s="94" customFormat="1">
+      <c r="A29" s="102">
         <v>45001</v>
       </c>
-      <c r="B29" s="115">
+      <c r="B29" s="103">
         <v>58.48</v>
       </c>
-      <c r="C29" s="116" t="s">
+      <c r="C29" s="104" t="s">
         <v>788</v>
       </c>
-      <c r="D29" s="117" t="s">
+      <c r="D29" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="117" t="s">
+      <c r="E29" s="105" t="s">
         <v>543</v>
       </c>
-      <c r="F29" s="117"/>
-    </row>
-    <row r="30" spans="1:6" s="99" customFormat="1">
-      <c r="A30" s="114">
+      <c r="F29" s="105"/>
+    </row>
+    <row r="30" spans="1:6" s="94" customFormat="1">
+      <c r="A30" s="102">
         <v>45001</v>
       </c>
-      <c r="B30" s="115">
+      <c r="B30" s="103">
         <v>3.99</v>
       </c>
-      <c r="C30" s="116">
+      <c r="C30" s="104">
         <v>330</v>
       </c>
-      <c r="D30" s="117" t="s">
+      <c r="D30" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="117" t="s">
+      <c r="E30" s="105" t="s">
         <v>817</v>
       </c>
-      <c r="F30" s="117" t="s">
+      <c r="F30" s="105" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="99" customFormat="1">
-      <c r="A31" s="114">
+    <row r="31" spans="1:6" s="94" customFormat="1">
+      <c r="A31" s="102">
         <v>45001</v>
       </c>
-      <c r="B31" s="115">
+      <c r="B31" s="103">
         <v>9.73</v>
       </c>
-      <c r="C31" s="116">
+      <c r="C31" s="104">
         <v>804</v>
       </c>
-      <c r="D31" s="117" t="s">
+      <c r="D31" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E31" s="117" t="s">
+      <c r="E31" s="105" t="s">
         <v>818</v>
       </c>
-      <c r="F31" s="117" t="s">
+      <c r="F31" s="105" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="99" customFormat="1">
-      <c r="A32" s="114">
+    <row r="32" spans="1:6" s="94" customFormat="1">
+      <c r="A32" s="102">
         <v>45002</v>
       </c>
-      <c r="B32" s="115">
+      <c r="B32" s="103">
         <v>3.34</v>
       </c>
-      <c r="C32" s="116">
+      <c r="C32" s="104">
         <v>276</v>
       </c>
-      <c r="D32" s="117" t="s">
+      <c r="D32" s="105" t="s">
         <v>819</v>
       </c>
-      <c r="E32" s="117" t="s">
+      <c r="E32" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="117" t="s">
+      <c r="F32" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="99" customFormat="1">
-      <c r="A33" s="114">
+    <row r="33" spans="1:6" s="94" customFormat="1">
+      <c r="A33" s="102">
         <v>45002</v>
       </c>
-      <c r="B33" s="115">
+      <c r="B33" s="103">
         <v>15.75</v>
       </c>
-      <c r="C33" s="116">
+      <c r="C33" s="104">
         <v>1300</v>
       </c>
-      <c r="D33" s="117" t="s">
+      <c r="D33" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="117" t="s">
+      <c r="E33" s="105" t="s">
         <v>820</v>
       </c>
-      <c r="F33" s="117" t="s">
+      <c r="F33" s="105" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="99" customFormat="1">
-      <c r="A34" s="114">
+    <row r="34" spans="1:6" s="94" customFormat="1">
+      <c r="A34" s="102">
         <v>45002</v>
       </c>
-      <c r="B34" s="115">
+      <c r="B34" s="103">
         <v>4</v>
       </c>
-      <c r="C34" s="116">
+      <c r="C34" s="104">
         <v>330</v>
       </c>
-      <c r="D34" s="117" t="s">
+      <c r="D34" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117" t="s">
+      <c r="E34" s="105"/>
+      <c r="F34" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="99" customFormat="1">
-      <c r="A35" s="114">
+    <row r="35" spans="1:6" s="94" customFormat="1">
+      <c r="A35" s="102">
         <v>45002</v>
       </c>
-      <c r="B35" s="115">
+      <c r="B35" s="103">
         <v>5.59</v>
       </c>
-      <c r="C35" s="116">
+      <c r="C35" s="104">
         <v>461</v>
       </c>
-      <c r="D35" s="117" t="s">
+      <c r="D35" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117" t="s">
+      <c r="E35" s="105"/>
+      <c r="F35" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="99" customFormat="1">
-      <c r="A36" s="114">
+    <row r="36" spans="1:6" s="94" customFormat="1">
+      <c r="A36" s="102">
         <v>45002</v>
       </c>
-      <c r="B36" s="115">
+      <c r="B36" s="103">
         <v>6.05</v>
       </c>
-      <c r="C36" s="116">
+      <c r="C36" s="104">
         <v>499</v>
       </c>
-      <c r="D36" s="117" t="s">
+      <c r="D36" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117" t="s">
+      <c r="E36" s="105"/>
+      <c r="F36" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="99" customFormat="1">
-      <c r="A37" s="114">
+    <row r="37" spans="1:6" s="94" customFormat="1">
+      <c r="A37" s="102">
         <v>45002</v>
       </c>
-      <c r="B37" s="115">
+      <c r="B37" s="103">
         <v>3.34</v>
       </c>
-      <c r="C37" s="116">
+      <c r="C37" s="104">
         <v>854</v>
       </c>
-      <c r="D37" s="117" t="s">
+      <c r="D37" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117" t="s">
+      <c r="E37" s="105"/>
+      <c r="F37" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="99" customFormat="1">
-      <c r="A38" s="114">
+    <row r="38" spans="1:6" s="94" customFormat="1">
+      <c r="A38" s="102">
         <v>45002</v>
       </c>
-      <c r="B38" s="115">
+      <c r="B38" s="103">
         <v>12.09</v>
       </c>
-      <c r="C38" s="116">
+      <c r="C38" s="104">
         <v>276</v>
       </c>
-      <c r="D38" s="117" t="s">
+      <c r="D38" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117" t="s">
+      <c r="E38" s="105"/>
+      <c r="F38" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="99" customFormat="1">
-      <c r="A39" s="114">
+    <row r="39" spans="1:6" s="94" customFormat="1">
+      <c r="A39" s="102">
         <v>45004</v>
       </c>
-      <c r="B39" s="115">
+      <c r="B39" s="103">
         <v>7.55</v>
       </c>
-      <c r="C39" s="116" t="s">
+      <c r="C39" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="D39" s="117" t="s">
+      <c r="D39" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="117" t="s">
+      <c r="E39" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="F39" s="117" t="s">
+      <c r="F39" s="105" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="99" customFormat="1">
-      <c r="A40" s="114">
+    <row r="40" spans="1:6" s="94" customFormat="1">
+      <c r="A40" s="102">
         <v>45005</v>
       </c>
-      <c r="B40" s="115">
+      <c r="B40" s="103">
         <v>13.16</v>
       </c>
-      <c r="C40" s="116">
+      <c r="C40" s="104">
         <v>1086</v>
       </c>
-      <c r="D40" s="117" t="s">
+      <c r="D40" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="117" t="s">
+      <c r="E40" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="F40" s="117" t="s">
+      <c r="F40" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="99" customFormat="1">
-      <c r="A41" s="114">
+    <row r="41" spans="1:6" s="94" customFormat="1">
+      <c r="A41" s="102">
         <v>45005</v>
       </c>
-      <c r="B41" s="115">
+      <c r="B41" s="103">
         <v>15.75</v>
       </c>
-      <c r="C41" s="116">
+      <c r="C41" s="104">
         <v>1300</v>
       </c>
-      <c r="D41" s="117" t="s">
+      <c r="D41" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="117" t="s">
+      <c r="E41" s="105" t="s">
         <v>820</v>
       </c>
-      <c r="F41" s="117" t="s">
+      <c r="F41" s="105" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="99" customFormat="1">
-      <c r="A42" s="114">
+    <row r="42" spans="1:6" s="94" customFormat="1">
+      <c r="A42" s="102">
         <v>45005</v>
       </c>
-      <c r="B42" s="115">
+      <c r="B42" s="103">
         <v>23.99</v>
       </c>
-      <c r="C42" s="116">
+      <c r="C42" s="104">
         <v>1980</v>
       </c>
-      <c r="D42" s="117" t="s">
+      <c r="D42" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="117" t="s">
+      <c r="E42" s="105" t="s">
         <v>822</v>
       </c>
-      <c r="F42" s="117" t="s">
+      <c r="F42" s="105" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="99" customFormat="1">
-      <c r="A43" s="114">
+    <row r="43" spans="1:6" s="94" customFormat="1">
+      <c r="A43" s="102">
         <v>45005</v>
       </c>
-      <c r="B43" s="115">
+      <c r="B43" s="103">
         <v>33.61</v>
       </c>
-      <c r="C43" s="116">
+      <c r="C43" s="104">
         <v>2774</v>
       </c>
-      <c r="D43" s="117" t="s">
+      <c r="D43" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="117"/>
-      <c r="F43" s="117"/>
-    </row>
-    <row r="44" spans="1:6" s="99" customFormat="1">
-      <c r="A44" s="114">
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+    </row>
+    <row r="44" spans="1:6" s="94" customFormat="1">
+      <c r="A44" s="102">
         <v>45005</v>
       </c>
-      <c r="B44" s="115">
+      <c r="B44" s="103">
         <v>14.48</v>
       </c>
-      <c r="C44" s="116">
+      <c r="C44" s="104">
         <v>1195</v>
       </c>
-      <c r="D44" s="117" t="s">
+      <c r="D44" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="117" t="s">
+      <c r="E44" s="105" t="s">
         <v>823</v>
       </c>
-      <c r="F44" s="117" t="s">
+      <c r="F44" s="105" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="99" customFormat="1">
-      <c r="A45" s="114">
+    <row r="45" spans="1:6" s="94" customFormat="1">
+      <c r="A45" s="102">
         <v>45006</v>
       </c>
-      <c r="B45" s="115">
+      <c r="B45" s="103">
         <v>11.12</v>
       </c>
-      <c r="C45" s="116">
+      <c r="C45" s="104">
         <v>918</v>
       </c>
-      <c r="D45" s="117" t="s">
+      <c r="D45" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="117" t="s">
+      <c r="E45" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="F45" s="117" t="s">
+      <c r="F45" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:6" s="99" customFormat="1">
-      <c r="A46" s="114">
+    <row r="46" spans="1:6" s="94" customFormat="1">
+      <c r="A46" s="102">
         <v>45006</v>
       </c>
-      <c r="B46" s="115">
+      <c r="B46" s="103">
         <v>69.5</v>
       </c>
-      <c r="C46" s="116">
+      <c r="C46" s="104">
         <v>5750</v>
       </c>
-      <c r="D46" s="117" t="s">
+      <c r="D46" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E46" s="117" t="s">
+      <c r="E46" s="105" t="s">
         <v>603</v>
       </c>
-      <c r="F46" s="117" t="s">
+      <c r="F46" s="105" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="99" customFormat="1">
-      <c r="A47" s="114">
+    <row r="47" spans="1:6" s="94" customFormat="1">
+      <c r="A47" s="102">
         <v>45006</v>
       </c>
-      <c r="B47" s="115">
+      <c r="B47" s="103">
         <v>30.24</v>
       </c>
-      <c r="C47" s="116">
+      <c r="C47" s="104">
         <v>2500</v>
       </c>
-      <c r="D47" s="117" t="s">
+      <c r="D47" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E47" s="117" t="s">
+      <c r="E47" s="105" t="s">
         <v>825</v>
       </c>
-      <c r="F47" s="117" t="s">
+      <c r="F47" s="105" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="99" customFormat="1">
-      <c r="A48" s="114">
+    <row r="48" spans="1:6" s="94" customFormat="1">
+      <c r="A48" s="102">
         <v>45006</v>
       </c>
-      <c r="B48" s="115">
+      <c r="B48" s="103">
         <v>30.56</v>
       </c>
-      <c r="C48" s="116">
+      <c r="C48" s="104">
         <v>2527</v>
       </c>
-      <c r="D48" s="117" t="s">
+      <c r="D48" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E48" s="117" t="s">
+      <c r="E48" s="105" t="s">
         <v>604</v>
       </c>
-      <c r="F48" s="117" t="s">
+      <c r="F48" s="105" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="99" customFormat="1">
-      <c r="A49" s="114">
+    <row r="49" spans="1:6" s="94" customFormat="1">
+      <c r="A49" s="102">
         <v>45046</v>
       </c>
-      <c r="B49" s="115"/>
-      <c r="C49" s="116">
+      <c r="B49" s="103"/>
+      <c r="C49" s="104">
         <v>1500</v>
       </c>
-      <c r="D49" s="117" t="s">
+      <c r="D49" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="117" t="s">
+      <c r="E49" s="105" t="s">
         <v>1107</v>
       </c>
-      <c r="F49" s="117" t="s">
+      <c r="F49" s="105" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="99" customFormat="1">
-      <c r="A50" s="114">
+    <row r="50" spans="1:6" s="94" customFormat="1">
+      <c r="A50" s="102">
         <v>45006</v>
       </c>
-      <c r="B50" s="115">
+      <c r="B50" s="103">
         <v>1.21</v>
       </c>
-      <c r="C50" s="116">
+      <c r="C50" s="104">
         <v>100</v>
       </c>
-      <c r="D50" s="117" t="s">
+      <c r="D50" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E50" s="117" t="s">
+      <c r="E50" s="105" t="s">
         <v>827</v>
       </c>
-      <c r="F50" s="117" t="s">
+      <c r="F50" s="105" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="99" customFormat="1">
-      <c r="A51" s="118">
+    <row r="51" spans="1:6" s="94" customFormat="1">
+      <c r="A51" s="106">
         <v>45058</v>
       </c>
-      <c r="B51" s="100">
+      <c r="B51" s="95">
         <v>4.8899999999999997</v>
       </c>
-      <c r="C51" s="100">
+      <c r="C51" s="95">
         <v>402</v>
       </c>
-      <c r="D51" s="99" t="s">
+      <c r="D51" s="94" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="99" t="s">
+      <c r="E51" s="94" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="99" customFormat="1">
-      <c r="A52" s="114">
+    <row r="52" spans="1:6" s="94" customFormat="1">
+      <c r="A52" s="102">
         <v>45012</v>
       </c>
-      <c r="B52" s="115">
+      <c r="B52" s="103">
         <v>117.34</v>
       </c>
-      <c r="C52" s="116">
+      <c r="C52" s="104">
         <v>9650</v>
       </c>
-      <c r="D52" s="117" t="s">
+      <c r="D52" s="105" t="s">
         <v>786</v>
       </c>
-      <c r="E52" s="117" t="s">
+      <c r="E52" s="105" t="s">
         <v>828</v>
       </c>
-      <c r="F52" s="117" t="s">
+      <c r="F52" s="105" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="53" spans="1:6" s="99" customFormat="1">
-      <c r="A53" s="114">
+    <row r="53" spans="1:6" s="94" customFormat="1">
+      <c r="A53" s="102">
         <v>45196</v>
       </c>
-      <c r="B53" s="115">
+      <c r="B53" s="103">
         <v>4.24</v>
       </c>
-      <c r="C53" s="116">
+      <c r="C53" s="104">
         <v>352.82</v>
       </c>
-      <c r="D53" s="117" t="s">
+      <c r="D53" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="E53" s="117" t="s">
+      <c r="E53" s="105" t="s">
         <v>896</v>
       </c>
-      <c r="F53" s="117" t="s">
+      <c r="F53" s="105" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="54" spans="1:6" s="99" customFormat="1">
-      <c r="A54" s="114"/>
-      <c r="B54" s="115"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="117"/>
-      <c r="F54" s="117"/>
-    </row>
-    <row r="55" spans="1:6" s="99" customFormat="1">
-      <c r="A55" s="114">
+    <row r="54" spans="1:6" s="94" customFormat="1">
+      <c r="A54" s="102"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="104"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="105"/>
+    </row>
+    <row r="55" spans="1:6" s="94" customFormat="1">
+      <c r="A55" s="102">
         <v>45225</v>
       </c>
-      <c r="B55" s="115">
+      <c r="B55" s="103">
         <v>69.53</v>
       </c>
-      <c r="C55" s="116">
+      <c r="C55" s="104">
         <v>5800</v>
       </c>
-      <c r="D55" s="117" t="s">
+      <c r="D55" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E55" s="117" t="s">
+      <c r="E55" s="105" t="s">
         <v>830</v>
       </c>
-      <c r="F55" s="117" t="s">
+      <c r="F55" s="105" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="56" spans="1:6" s="99" customFormat="1">
-      <c r="A56" s="114">
+    <row r="56" spans="1:6" s="94" customFormat="1">
+      <c r="A56" s="102">
         <v>45250</v>
       </c>
-      <c r="B56" s="115">
+      <c r="B56" s="103">
         <v>24.6</v>
       </c>
-      <c r="C56" s="116">
+      <c r="C56" s="104">
         <v>2050</v>
       </c>
-      <c r="D56" s="117" t="s">
+      <c r="D56" s="105" t="s">
         <v>188</v>
       </c>
-      <c r="E56" s="117" t="s">
+      <c r="E56" s="105" t="s">
         <v>544</v>
       </c>
-      <c r="F56" s="117" t="s">
+      <c r="F56" s="105" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="57" spans="1:6" s="99" customFormat="1">
-      <c r="A57" s="114">
+    <row r="57" spans="1:6" s="94" customFormat="1">
+      <c r="A57" s="102">
         <v>45292</v>
       </c>
-      <c r="B57" s="115"/>
-      <c r="C57" s="116">
+      <c r="B57" s="103"/>
+      <c r="C57" s="104">
         <v>156</v>
       </c>
-      <c r="D57" s="117" t="s">
+      <c r="D57" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="E57" s="117" t="s">
+      <c r="E57" s="105" t="s">
         <v>1101</v>
       </c>
-      <c r="F57" s="117" t="s">
+      <c r="F57" s="105" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="123" customFormat="1">
-      <c r="A58" s="119">
+    <row r="58" spans="1:6" s="111" customFormat="1">
+      <c r="A58" s="107">
         <v>45295</v>
       </c>
-      <c r="B58" s="120">
+      <c r="B58" s="108">
         <v>60.07</v>
       </c>
-      <c r="C58" s="121">
+      <c r="C58" s="109">
         <v>5000</v>
       </c>
-      <c r="D58" s="122" t="s">
+      <c r="D58" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="E58" s="122" t="s">
+      <c r="E58" s="110" t="s">
         <v>833</v>
       </c>
-      <c r="F58" s="122" t="s">
+      <c r="F58" s="110" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="59" spans="1:6" s="123" customFormat="1">
-      <c r="A59" s="119">
+    <row r="59" spans="1:6" s="111" customFormat="1">
+      <c r="A59" s="107">
         <v>45410</v>
       </c>
-      <c r="B59" s="120">
+      <c r="B59" s="108">
         <v>67.150000000000006</v>
       </c>
-      <c r="C59" s="121">
+      <c r="C59" s="109">
         <v>5600</v>
       </c>
-      <c r="D59" s="122" t="s">
+      <c r="D59" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="122" t="s">
+      <c r="E59" s="110" t="s">
         <v>679</v>
       </c>
-      <c r="F59" s="122" t="s">
+      <c r="F59" s="110" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="60" spans="1:6" s="123" customFormat="1">
-      <c r="A60" s="119">
+    <row r="60" spans="1:6" s="111" customFormat="1">
+      <c r="A60" s="107">
         <v>45604</v>
       </c>
-      <c r="B60" s="120">
+      <c r="B60" s="108">
         <v>26.07</v>
       </c>
-      <c r="C60" s="121">
+      <c r="C60" s="109">
         <v>2200</v>
       </c>
-      <c r="D60" s="122" t="s">
+      <c r="D60" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="E60" s="122" t="s">
+      <c r="E60" s="110" t="s">
         <v>835</v>
       </c>
-      <c r="F60" s="122" t="s">
+      <c r="F60" s="110" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="61" spans="1:6" s="123" customFormat="1">
-      <c r="A61" s="119">
+    <row r="61" spans="1:6" s="111" customFormat="1">
+      <c r="A61" s="107">
         <v>45614</v>
       </c>
-      <c r="B61" s="120">
+      <c r="B61" s="108">
         <v>50.36</v>
       </c>
-      <c r="C61" s="121">
+      <c r="C61" s="109">
         <v>4250</v>
       </c>
-      <c r="D61" s="122" t="s">
+      <c r="D61" s="110" t="s">
         <v>261</v>
       </c>
-      <c r="E61" s="122" t="s">
+      <c r="E61" s="110" t="s">
         <v>836</v>
       </c>
-      <c r="F61" s="122" t="s">
+      <c r="F61" s="110" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="62" spans="1:6" s="123" customFormat="1">
-      <c r="A62" s="119">
+    <row r="62" spans="1:6" s="111" customFormat="1">
+      <c r="A62" s="107">
         <v>45620</v>
       </c>
-      <c r="B62" s="120">
+      <c r="B62" s="108">
         <v>7.32</v>
       </c>
-      <c r="C62" s="121">
+      <c r="C62" s="109">
         <v>618</v>
       </c>
-      <c r="D62" s="122" t="s">
+      <c r="D62" s="110" t="s">
         <v>837</v>
       </c>
-      <c r="E62" s="122" t="s">
+      <c r="E62" s="110" t="s">
         <v>796</v>
       </c>
-      <c r="F62" s="122" t="s">
+      <c r="F62" s="110" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="63" spans="1:6" s="123" customFormat="1">
-      <c r="A63" s="119">
+    <row r="63" spans="1:6" s="111" customFormat="1">
+      <c r="A63" s="107">
         <v>45622</v>
       </c>
-      <c r="B63" s="120">
+      <c r="B63" s="108">
         <v>83.04</v>
       </c>
-      <c r="C63" s="121">
+      <c r="C63" s="109">
         <v>7000</v>
       </c>
-      <c r="D63" s="122" t="s">
+      <c r="D63" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="E63" s="122" t="s">
+      <c r="E63" s="110" t="s">
         <v>838</v>
       </c>
-      <c r="F63" s="122" t="s">
+      <c r="F63" s="110" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="64" spans="1:6" s="123" customFormat="1">
-      <c r="A64" s="119">
+    <row r="64" spans="1:6" s="111" customFormat="1">
+      <c r="A64" s="107">
         <v>45626</v>
       </c>
-      <c r="B64" s="120">
+      <c r="B64" s="108">
         <v>66</v>
       </c>
-      <c r="C64" s="121" t="s">
+      <c r="C64" s="109" t="s">
         <v>789</v>
       </c>
-      <c r="D64" s="122" t="s">
+      <c r="D64" s="110" t="s">
         <v>261</v>
       </c>
-      <c r="E64" s="122" t="s">
+      <c r="E64" s="110" t="s">
         <v>540</v>
       </c>
-      <c r="F64" s="122" t="s">
+      <c r="F64" s="110" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="123" customFormat="1">
-      <c r="A65" s="119">
+    <row r="65" spans="1:6" s="111" customFormat="1">
+      <c r="A65" s="107">
         <v>45630</v>
       </c>
-      <c r="B65" s="120">
+      <c r="B65" s="108">
         <v>49.58</v>
       </c>
-      <c r="C65" s="121">
+      <c r="C65" s="109">
         <v>4200</v>
       </c>
-      <c r="D65" s="122" t="s">
+      <c r="D65" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="E65" s="122" t="s">
+      <c r="E65" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="F65" s="122" t="s">
+      <c r="F65" s="110" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="123" customFormat="1">
-      <c r="A66" s="119">
+    <row r="66" spans="1:6" s="111" customFormat="1">
+      <c r="A66" s="107">
         <v>45631</v>
       </c>
-      <c r="B66" s="120">
+      <c r="B66" s="108">
         <v>23.62</v>
       </c>
-      <c r="C66" s="121">
+      <c r="C66" s="109">
         <v>2000</v>
       </c>
-      <c r="D66" s="122" t="s">
+      <c r="D66" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="E66" s="122" t="s">
+      <c r="E66" s="110" t="s">
         <v>201</v>
       </c>
-      <c r="F66" s="122" t="s">
+      <c r="F66" s="110" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="123" customFormat="1">
-      <c r="A67" s="119">
+    <row r="67" spans="1:6" s="111" customFormat="1">
+      <c r="A67" s="107">
         <v>45632</v>
       </c>
-      <c r="B67" s="120">
+      <c r="B67" s="108">
         <v>4.72</v>
       </c>
-      <c r="C67" s="121">
+      <c r="C67" s="109">
         <v>400</v>
       </c>
-      <c r="D67" s="122" t="s">
+      <c r="D67" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="E67" s="122" t="s">
+      <c r="E67" s="110" t="s">
         <v>840</v>
       </c>
-      <c r="F67" s="122" t="s">
+      <c r="F67" s="110" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="123" customFormat="1">
-      <c r="A68" s="119">
+    <row r="68" spans="1:6" s="111" customFormat="1">
+      <c r="A68" s="107">
         <v>45634</v>
       </c>
-      <c r="B68" s="120">
+      <c r="B68" s="108">
         <v>563</v>
       </c>
-      <c r="C68" s="121">
+      <c r="C68" s="109">
         <v>50000</v>
       </c>
-      <c r="D68" s="122" t="s">
+      <c r="D68" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="E68" s="122" t="s">
+      <c r="E68" s="110" t="s">
         <v>842</v>
       </c>
-      <c r="F68" s="122" t="s">
+      <c r="F68" s="110" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="123" customFormat="1">
-      <c r="A69" s="119">
+    <row r="69" spans="1:6" s="111" customFormat="1">
+      <c r="A69" s="107">
         <v>45640</v>
       </c>
-      <c r="B69" s="120">
+      <c r="B69" s="108">
         <v>23.6</v>
       </c>
-      <c r="C69" s="121">
+      <c r="C69" s="109">
         <v>2000</v>
       </c>
-      <c r="D69" s="122" t="s">
+      <c r="D69" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="E69" s="122" t="s">
+      <c r="E69" s="110" t="s">
         <v>844</v>
       </c>
-      <c r="F69" s="122" t="s">
+      <c r="F69" s="110" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="123" customFormat="1">
-      <c r="A70" s="119">
+    <row r="70" spans="1:6" s="111" customFormat="1">
+      <c r="A70" s="107">
         <v>45643</v>
       </c>
-      <c r="B70" s="120">
+      <c r="B70" s="108">
         <v>22.9</v>
       </c>
-      <c r="C70" s="121">
+      <c r="C70" s="109">
         <v>2200</v>
       </c>
-      <c r="D70" s="122" t="s">
+      <c r="D70" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="E70" s="122" t="s">
+      <c r="E70" s="110" t="s">
         <v>846</v>
       </c>
-      <c r="F70" s="122" t="s">
+      <c r="F70" s="110" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="96" customFormat="1">
-      <c r="A71" s="124">
+    <row r="71" spans="1:6" s="91" customFormat="1">
+      <c r="A71" s="112">
         <v>45772</v>
       </c>
-      <c r="B71" s="125">
+      <c r="B71" s="113">
         <v>5.64</v>
       </c>
-      <c r="C71" s="126">
+      <c r="C71" s="114">
         <v>2025</v>
       </c>
-      <c r="D71" s="127" t="s">
+      <c r="D71" s="115" t="s">
         <v>237</v>
       </c>
-      <c r="E71" s="127" t="s">
+      <c r="E71" s="115" t="s">
         <v>848</v>
       </c>
-      <c r="F71" s="127" t="s">
+      <c r="F71" s="115" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="96" customFormat="1">
-      <c r="A72" s="124">
+    <row r="72" spans="1:6" s="91" customFormat="1">
+      <c r="A72" s="112">
         <v>45885</v>
       </c>
-      <c r="B72" s="125">
+      <c r="B72" s="113">
         <v>168</v>
       </c>
-      <c r="C72" s="126">
+      <c r="C72" s="114">
         <v>16095</v>
       </c>
-      <c r="D72" s="127" t="s">
+      <c r="D72" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="127" t="s">
+      <c r="E72" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="F72" s="127" t="s">
+      <c r="F72" s="115" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="1:6" s="96" customFormat="1">
-      <c r="A73" s="124">
+    <row r="73" spans="1:6" s="91" customFormat="1">
+      <c r="A73" s="112">
         <v>45885</v>
       </c>
-      <c r="B73" s="125">
+      <c r="B73" s="113">
         <v>168</v>
       </c>
-      <c r="C73" s="126">
+      <c r="C73" s="114">
         <v>16095</v>
       </c>
-      <c r="D73" s="127" t="s">
+      <c r="D73" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="E73" s="127" t="s">
+      <c r="E73" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="F73" s="127" t="s">
+      <c r="F73" s="115" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:6" s="96" customFormat="1">
-      <c r="A74" s="124">
+    <row r="74" spans="1:6" s="91" customFormat="1">
+      <c r="A74" s="112">
         <v>45885</v>
       </c>
-      <c r="B74" s="125">
+      <c r="B74" s="113">
         <v>169</v>
       </c>
-      <c r="C74" s="126">
+      <c r="C74" s="114">
         <v>16095</v>
       </c>
-      <c r="D74" s="127" t="s">
+      <c r="D74" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="E74" s="127" t="s">
+      <c r="E74" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="F74" s="127" t="s">
+      <c r="F74" s="115" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="75" spans="1:6" s="96" customFormat="1">
-      <c r="A75" s="124">
+    <row r="75" spans="1:6" s="91" customFormat="1">
+      <c r="A75" s="112">
         <v>45891</v>
       </c>
-      <c r="B75" s="125">
+      <c r="B75" s="113">
         <v>117</v>
       </c>
-      <c r="C75" s="126">
+      <c r="C75" s="114">
         <v>10218</v>
       </c>
-      <c r="D75" s="127" t="s">
+      <c r="D75" s="115" t="s">
         <v>236</v>
       </c>
-      <c r="E75" s="127" t="s">
+      <c r="E75" s="115" t="s">
         <v>850</v>
       </c>
-      <c r="F75" s="127" t="s">
+      <c r="F75" s="115" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="76" spans="1:6" s="96" customFormat="1">
-      <c r="A76" s="124">
+    <row r="76" spans="1:6" s="91" customFormat="1">
+      <c r="A76" s="112">
         <v>45907</v>
       </c>
-      <c r="B76" s="125">
+      <c r="B76" s="113">
         <v>112.56</v>
       </c>
-      <c r="C76" s="126">
+      <c r="C76" s="114">
         <v>10000</v>
       </c>
-      <c r="D76" s="127" t="s">
+      <c r="D76" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E76" s="127" t="s">
+      <c r="E76" s="115" t="s">
         <v>852</v>
       </c>
-      <c r="F76" s="127" t="s">
+      <c r="F76" s="115" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="77" spans="1:6" s="96" customFormat="1">
-      <c r="A77" s="124">
+    <row r="77" spans="1:6" s="91" customFormat="1">
+      <c r="A77" s="112">
         <v>45908</v>
       </c>
-      <c r="B77" s="125"/>
-      <c r="C77" s="126">
+      <c r="B77" s="113"/>
+      <c r="C77" s="114">
         <v>1000</v>
       </c>
-      <c r="D77" s="127" t="s">
+      <c r="D77" s="115" t="s">
         <v>1076</v>
       </c>
-      <c r="E77" s="127" t="s">
+      <c r="E77" s="115" t="s">
         <v>1077</v>
       </c>
-      <c r="F77" s="127" t="s">
+      <c r="F77" s="115" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="78" spans="1:6" s="96" customFormat="1">
-      <c r="A78" s="124">
+    <row r="78" spans="1:6" s="91" customFormat="1">
+      <c r="A78" s="112">
         <v>45909</v>
       </c>
-      <c r="B78" s="125">
+      <c r="B78" s="113">
         <v>21.87</v>
       </c>
-      <c r="C78" s="126">
+      <c r="C78" s="114">
         <v>1930</v>
       </c>
-      <c r="D78" s="127" t="s">
+      <c r="D78" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E78" s="127" t="s">
+      <c r="E78" s="115" t="s">
         <v>854</v>
       </c>
-      <c r="F78" s="127" t="s">
+      <c r="F78" s="115" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="79" spans="1:6" s="96" customFormat="1">
-      <c r="A79" s="124">
+    <row r="79" spans="1:6" s="91" customFormat="1">
+      <c r="A79" s="112">
         <v>45909</v>
       </c>
-      <c r="B79" s="125">
+      <c r="B79" s="113">
         <v>22.66</v>
       </c>
-      <c r="C79" s="126">
+      <c r="C79" s="114">
         <v>2000</v>
       </c>
-      <c r="D79" s="127" t="s">
+      <c r="D79" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="E79" s="127" t="s">
+      <c r="E79" s="115" t="s">
         <v>854</v>
       </c>
-      <c r="F79" s="127" t="s">
+      <c r="F79" s="115" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="80" spans="1:6" s="96" customFormat="1">
-      <c r="A80" s="124">
+    <row r="80" spans="1:6" s="91" customFormat="1">
+      <c r="A80" s="112">
         <v>45917</v>
       </c>
-      <c r="B80" s="125">
+      <c r="B80" s="113">
         <v>57.06</v>
       </c>
-      <c r="C80" s="126">
+      <c r="C80" s="114">
         <v>5017</v>
       </c>
-      <c r="D80" s="127" t="s">
+      <c r="D80" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="E80" s="127" t="s">
+      <c r="E80" s="115" t="s">
         <v>856</v>
       </c>
-      <c r="F80" s="127" t="s">
+      <c r="F80" s="115" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="81" spans="1:6" s="96" customFormat="1">
-      <c r="A81" s="124">
+    <row r="81" spans="1:6" s="91" customFormat="1">
+      <c r="A81" s="112">
         <v>45923</v>
       </c>
-      <c r="B81" s="125">
+      <c r="B81" s="113">
         <v>90.08</v>
       </c>
-      <c r="C81" s="126">
+      <c r="C81" s="114">
         <v>8000</v>
       </c>
-      <c r="D81" s="127" t="s">
+      <c r="D81" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E81" s="127" t="s">
+      <c r="E81" s="115" t="s">
         <v>259</v>
       </c>
-      <c r="F81" s="127" t="s">
+      <c r="F81" s="115" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="82" spans="1:6" s="96" customFormat="1">
-      <c r="A82" s="124">
+    <row r="82" spans="1:6" s="91" customFormat="1">
+      <c r="A82" s="112">
         <v>45924</v>
       </c>
-      <c r="B82" s="125">
+      <c r="B82" s="113">
         <v>9.57</v>
       </c>
-      <c r="C82" s="126">
+      <c r="C82" s="114">
         <v>850</v>
       </c>
-      <c r="D82" s="127" t="s">
+      <c r="D82" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E82" s="127" t="s">
+      <c r="E82" s="115" t="s">
         <v>840</v>
       </c>
-      <c r="F82" s="127" t="s">
+      <c r="F82" s="115" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="83" spans="1:6" s="96" customFormat="1">
-      <c r="A83" s="124">
+    <row r="83" spans="1:6" s="91" customFormat="1">
+      <c r="A83" s="112">
         <v>45971</v>
       </c>
-      <c r="B83" s="125">
+      <c r="B83" s="113">
         <v>18.04</v>
       </c>
-      <c r="C83" s="126">
+      <c r="C83" s="114">
         <v>1600</v>
       </c>
-      <c r="D83" s="127" t="s">
+      <c r="D83" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E83" s="127" t="s">
+      <c r="E83" s="115" t="s">
         <v>1079</v>
       </c>
-      <c r="F83" s="127" t="s">
+      <c r="F83" s="115" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="84" spans="1:6" s="96" customFormat="1">
-      <c r="A84" s="124">
+    <row r="84" spans="1:6" s="91" customFormat="1">
+      <c r="A84" s="112">
         <v>45971</v>
       </c>
-      <c r="B84" s="125">
+      <c r="B84" s="113">
         <v>563.65</v>
       </c>
-      <c r="C84" s="126">
+      <c r="C84" s="114">
         <v>50000</v>
       </c>
-      <c r="D84" s="127" t="s">
+      <c r="D84" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E84" s="127" t="s">
+      <c r="E84" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="F84" s="127" t="s">
+      <c r="F84" s="115" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="85" spans="1:6" s="96" customFormat="1">
-      <c r="A85" s="124">
+    <row r="85" spans="1:6" s="91" customFormat="1">
+      <c r="A85" s="112">
         <v>45972</v>
       </c>
-      <c r="B85" s="125">
+      <c r="B85" s="113">
         <v>349.22</v>
       </c>
-      <c r="C85" s="126">
+      <c r="C85" s="114">
         <v>30895</v>
       </c>
-      <c r="D85" s="127" t="s">
+      <c r="D85" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E85" s="127" t="s">
+      <c r="E85" s="115" t="s">
         <v>860</v>
       </c>
-      <c r="F85" s="127" t="s">
+      <c r="F85" s="115" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="86" spans="1:6" s="96" customFormat="1">
-      <c r="A86" s="124">
+    <row r="86" spans="1:6" s="91" customFormat="1">
+      <c r="A86" s="112">
         <v>45979</v>
       </c>
-      <c r="B86" s="125">
+      <c r="B86" s="113">
         <v>9.6</v>
       </c>
-      <c r="C86" s="126">
+      <c r="C86" s="114">
         <v>850</v>
       </c>
-      <c r="D86" s="127" t="s">
+      <c r="D86" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E86" s="127" t="s">
+      <c r="E86" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="F86" s="127" t="s">
+      <c r="F86" s="115" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="87" spans="1:6" s="96" customFormat="1">
-      <c r="A87" s="124">
+    <row r="87" spans="1:6" s="91" customFormat="1">
+      <c r="A87" s="112">
         <v>45980</v>
       </c>
-      <c r="B87" s="125">
+      <c r="B87" s="113">
         <v>1.86</v>
       </c>
-      <c r="C87" s="126">
+      <c r="C87" s="114">
         <v>165</v>
       </c>
-      <c r="D87" s="127" t="s">
+      <c r="D87" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E87" s="127" t="s">
+      <c r="E87" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="F87" s="127" t="s">
+      <c r="F87" s="115" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:6" s="96" customFormat="1">
-      <c r="A88" s="124">
+    <row r="88" spans="1:6" s="91" customFormat="1">
+      <c r="A88" s="112">
         <v>45980</v>
       </c>
-      <c r="B88" s="125">
+      <c r="B88" s="113">
         <v>18.66</v>
       </c>
-      <c r="C88" s="126">
+      <c r="C88" s="114">
         <v>1651</v>
       </c>
-      <c r="D88" s="127" t="s">
+      <c r="D88" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="E88" s="127" t="s">
+      <c r="E88" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="F88" s="127" t="s">
+      <c r="F88" s="115" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:6" s="96" customFormat="1">
-      <c r="A89" s="124">
+    <row r="89" spans="1:6" s="91" customFormat="1">
+      <c r="A89" s="112">
         <v>45982</v>
       </c>
-      <c r="B89" s="125">
+      <c r="B89" s="113">
         <v>37.9</v>
       </c>
-      <c r="C89" s="126">
+      <c r="C89" s="114">
         <v>3397</v>
       </c>
-      <c r="D89" s="127" t="s">
+      <c r="D89" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E89" s="127" t="s">
+      <c r="E89" s="115" t="s">
         <v>861</v>
       </c>
-      <c r="F89" s="127" t="s">
+      <c r="F89" s="115" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="90" spans="1:6" s="96" customFormat="1">
-      <c r="A90" s="124">
+    <row r="90" spans="1:6" s="91" customFormat="1">
+      <c r="A90" s="112">
         <v>45983</v>
       </c>
-      <c r="B90" s="125">
+      <c r="B90" s="113">
         <v>6.14</v>
       </c>
-      <c r="C90" s="126">
-        <v>550</v>
-      </c>
-      <c r="D90" s="127" t="s">
+      <c r="C90" s="114">
+        <v>550</v>
+      </c>
+      <c r="D90" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E90" s="127" t="s">
+      <c r="E90" s="115" t="s">
         <v>840</v>
       </c>
-      <c r="F90" s="127" t="s">
+      <c r="F90" s="115" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="91" spans="1:6" s="96" customFormat="1">
-      <c r="A91" s="124">
+    <row r="91" spans="1:6" s="91" customFormat="1">
+      <c r="A91" s="112">
         <v>45984</v>
       </c>
-      <c r="B91" s="125">
+      <c r="B91" s="113">
         <v>10.039999999999999</v>
       </c>
-      <c r="C91" s="126">
+      <c r="C91" s="114">
         <v>900</v>
       </c>
-      <c r="D91" s="127" t="s">
+      <c r="D91" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E91" s="127" t="s">
+      <c r="E91" s="115" t="s">
         <v>863</v>
       </c>
-      <c r="F91" s="127" t="s">
+      <c r="F91" s="115" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:6" s="96" customFormat="1">
-      <c r="A92" s="124">
+    <row r="92" spans="1:6" s="91" customFormat="1">
+      <c r="A92" s="112">
         <v>45991</v>
       </c>
-      <c r="B92" s="125">
+      <c r="B92" s="113">
         <v>179.11</v>
       </c>
-      <c r="C92" s="126">
+      <c r="C92" s="114">
         <v>16000</v>
       </c>
-      <c r="D92" s="127" t="s">
+      <c r="D92" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E92" s="127" t="s">
+      <c r="E92" s="115" t="s">
         <v>562</v>
       </c>
-      <c r="F92" s="127" t="s">
+      <c r="F92" s="115" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="93" spans="1:6" s="96" customFormat="1">
-      <c r="A93" s="124">
+    <row r="93" spans="1:6" s="91" customFormat="1">
+      <c r="A93" s="112">
         <v>45994</v>
       </c>
-      <c r="B93" s="125">
+      <c r="B93" s="113">
         <v>49.91</v>
       </c>
-      <c r="C93" s="126">
+      <c r="C93" s="114">
         <v>4500</v>
       </c>
-      <c r="D93" s="127" t="s">
+      <c r="D93" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E93" s="127" t="s">
+      <c r="E93" s="115" t="s">
         <v>260</v>
       </c>
-      <c r="F93" s="127" t="s">
+      <c r="F93" s="115" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="94" spans="1:6" s="96" customFormat="1">
-      <c r="A94" s="124">
+    <row r="94" spans="1:6" s="91" customFormat="1">
+      <c r="A94" s="112">
         <v>45998</v>
       </c>
-      <c r="B94" s="125">
+      <c r="B94" s="113">
         <v>16.690000000000001</v>
       </c>
-      <c r="C94" s="126">
+      <c r="C94" s="114">
         <v>1500</v>
       </c>
-      <c r="D94" s="127" t="s">
+      <c r="D94" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="E94" s="127" t="s">
+      <c r="E94" s="115" t="s">
         <v>865</v>
       </c>
-      <c r="F94" s="127" t="s">
+      <c r="F94" s="115" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="95" spans="1:6" s="96" customFormat="1">
-      <c r="A95" s="124">
+    <row r="95" spans="1:6" s="91" customFormat="1">
+      <c r="A95" s="112">
         <v>46007</v>
       </c>
-      <c r="B95" s="125">
+      <c r="B95" s="113">
         <v>43.98</v>
       </c>
-      <c r="C95" s="126">
+      <c r="C95" s="114">
         <v>4000</v>
       </c>
-      <c r="D95" s="127" t="s">
+      <c r="D95" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E95" s="127" t="s">
+      <c r="E95" s="115" t="s">
         <v>867</v>
       </c>
-      <c r="F95" s="127" t="s">
+      <c r="F95" s="115" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="96" spans="1:6" s="96" customFormat="1">
-      <c r="A96" s="124">
+    <row r="96" spans="1:6" s="91" customFormat="1">
+      <c r="A96" s="112">
         <v>46007</v>
       </c>
-      <c r="B96" s="125">
+      <c r="B96" s="113">
         <v>43.98</v>
       </c>
-      <c r="C96" s="126">
+      <c r="C96" s="114">
         <v>4000</v>
       </c>
-      <c r="D96" s="127" t="s">
+      <c r="D96" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E96" s="127" t="s">
+      <c r="E96" s="115" t="s">
         <v>867</v>
       </c>
-      <c r="F96" s="127" t="s">
+      <c r="F96" s="115" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="97" spans="1:6" s="96" customFormat="1">
-      <c r="A97" s="124">
+    <row r="97" spans="1:6" s="91" customFormat="1">
+      <c r="A97" s="112">
         <v>46008</v>
       </c>
-      <c r="B97" s="125">
+      <c r="B97" s="113">
         <v>552.9</v>
       </c>
-      <c r="C97" s="126">
+      <c r="C97" s="114">
         <v>50000</v>
       </c>
-      <c r="D97" s="127" t="s">
+      <c r="D97" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E97" s="127" t="s">
+      <c r="E97" s="115" t="s">
         <v>867</v>
       </c>
-      <c r="F97" s="127" t="s">
+      <c r="F97" s="115" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="98" spans="1:6" s="96" customFormat="1">
-      <c r="A98" s="124">
+    <row r="98" spans="1:6" s="91" customFormat="1">
+      <c r="A98" s="112">
         <v>46009</v>
       </c>
-      <c r="B98" s="125">
+      <c r="B98" s="113">
         <v>348.96</v>
       </c>
-      <c r="C98" s="126">
+      <c r="C98" s="114">
         <v>31500</v>
       </c>
-      <c r="D98" s="127" t="s">
+      <c r="D98" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E98" s="127" t="s">
+      <c r="E98" s="115" t="s">
         <v>867</v>
       </c>
-      <c r="F98" s="127" t="s">
+      <c r="F98" s="115" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="99" spans="1:6" s="96" customFormat="1">
-      <c r="A99" s="124">
+    <row r="99" spans="1:6" s="91" customFormat="1">
+      <c r="A99" s="112">
         <v>46009</v>
       </c>
-      <c r="B99" s="125">
+      <c r="B99" s="113">
         <v>14.4</v>
       </c>
-      <c r="C99" s="126">
+      <c r="C99" s="114">
         <v>1300</v>
       </c>
-      <c r="D99" s="127" t="s">
+      <c r="D99" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E99" s="127" t="s">
+      <c r="E99" s="115" t="s">
         <v>262</v>
       </c>
-      <c r="F99" s="127" t="s">
+      <c r="F99" s="115" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="100" spans="1:6" s="96" customFormat="1">
-      <c r="A100" s="124">
+    <row r="100" spans="1:6" s="91" customFormat="1">
+      <c r="A100" s="112">
         <v>46009</v>
       </c>
-      <c r="B100" s="125">
+      <c r="B100" s="113">
         <v>0.44</v>
       </c>
-      <c r="C100" s="126">
+      <c r="C100" s="114">
         <v>40</v>
       </c>
-      <c r="D100" s="127" t="s">
+      <c r="D100" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E100" s="127" t="s">
+      <c r="E100" s="115" t="s">
         <v>262</v>
       </c>
-      <c r="F100" s="127" t="s">
+      <c r="F100" s="115" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="101" spans="1:6" s="96" customFormat="1">
-      <c r="A101" s="124">
+    <row r="101" spans="1:6" s="91" customFormat="1">
+      <c r="A101" s="112">
         <v>46009</v>
       </c>
-      <c r="B101" s="125">
+      <c r="B101" s="113">
         <v>22.16</v>
       </c>
-      <c r="C101" s="126">
+      <c r="C101" s="114">
         <v>2000</v>
       </c>
-      <c r="D101" s="127" t="s">
+      <c r="D101" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E101" s="127" t="s">
+      <c r="E101" s="115" t="s">
         <v>872</v>
       </c>
-      <c r="F101" s="127" t="s">
+      <c r="F101" s="115" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="102" spans="1:6" s="96" customFormat="1">
-      <c r="A102" s="124">
+    <row r="102" spans="1:6" s="91" customFormat="1">
+      <c r="A102" s="112">
         <v>46010</v>
       </c>
-      <c r="B102" s="125">
+      <c r="B102" s="113">
         <v>81.38</v>
       </c>
-      <c r="C102" s="126">
+      <c r="C102" s="114">
         <v>7290</v>
       </c>
-      <c r="D102" s="127" t="s">
+      <c r="D102" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E102" s="127" t="s">
+      <c r="E102" s="115" t="s">
         <v>873</v>
       </c>
-      <c r="F102" s="127" t="s">
+      <c r="F102" s="115" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="103" spans="1:6" s="96" customFormat="1">
-      <c r="A103" s="124">
+    <row r="103" spans="1:6" s="91" customFormat="1">
+      <c r="A103" s="112">
         <v>46013</v>
       </c>
-      <c r="B103" s="125">
+      <c r="B103" s="113">
         <v>14.4</v>
       </c>
-      <c r="C103" s="126">
+      <c r="C103" s="114">
         <v>1290</v>
       </c>
-      <c r="D103" s="127" t="s">
+      <c r="D103" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E103" s="127" t="s">
+      <c r="E103" s="115" t="s">
         <v>875</v>
       </c>
-      <c r="F103" s="127" t="s">
+      <c r="F103" s="115" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="104" spans="1:6" s="96" customFormat="1">
-      <c r="A104" s="124">
+    <row r="104" spans="1:6" s="91" customFormat="1">
+      <c r="A104" s="112">
         <v>46013</v>
       </c>
-      <c r="B104" s="125">
+      <c r="B104" s="113">
         <v>3.91</v>
       </c>
-      <c r="C104" s="126">
+      <c r="C104" s="114">
         <v>350</v>
       </c>
-      <c r="D104" s="127" t="s">
+      <c r="D104" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E104" s="127" t="s">
+      <c r="E104" s="115" t="s">
         <v>269</v>
       </c>
-      <c r="F104" s="127" t="s">
+      <c r="F104" s="115" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="105" spans="1:6" s="96" customFormat="1">
-      <c r="A105" s="124">
+    <row r="105" spans="1:6" s="91" customFormat="1">
+      <c r="A105" s="112">
         <v>46013</v>
       </c>
-      <c r="B105" s="125">
+      <c r="B105" s="113">
         <v>68.08</v>
       </c>
-      <c r="C105" s="126">
+      <c r="C105" s="114">
         <v>6100</v>
       </c>
-      <c r="D105" s="127" t="s">
+      <c r="D105" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E105" s="127" t="s">
+      <c r="E105" s="115" t="s">
         <v>270</v>
       </c>
-      <c r="F105" s="127" t="s">
+      <c r="F105" s="115" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="106" spans="1:6" s="96" customFormat="1">
-      <c r="A106" s="124">
+    <row r="106" spans="1:6" s="91" customFormat="1">
+      <c r="A106" s="112">
         <v>46014</v>
       </c>
-      <c r="B106" s="125">
+      <c r="B106" s="113">
         <v>92.15</v>
       </c>
-      <c r="C106" s="126">
+      <c r="C106" s="114">
         <v>8245</v>
       </c>
-      <c r="D106" s="127" t="s">
+      <c r="D106" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E106" s="127" t="s">
+      <c r="E106" s="115" t="s">
         <v>877</v>
       </c>
-      <c r="F106" s="127" t="s">
+      <c r="F106" s="115" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="107" spans="1:6" s="96" customFormat="1">
-      <c r="A107" s="124">
+    <row r="107" spans="1:6" s="91" customFormat="1">
+      <c r="A107" s="112">
         <v>46015</v>
       </c>
-      <c r="B107" s="125">
+      <c r="B107" s="113">
         <v>94.63</v>
       </c>
-      <c r="C107" s="126">
+      <c r="C107" s="114">
         <v>8500</v>
       </c>
-      <c r="D107" s="127" t="s">
+      <c r="D107" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E107" s="127" t="s">
+      <c r="E107" s="115" t="s">
         <v>878</v>
       </c>
-      <c r="F107" s="127" t="s">
+      <c r="F107" s="115" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="108" spans="1:6" s="96" customFormat="1">
-      <c r="A108" s="124">
+    <row r="108" spans="1:6" s="91" customFormat="1">
+      <c r="A108" s="112">
         <v>46016</v>
       </c>
-      <c r="B108" s="125">
+      <c r="B108" s="113">
         <v>55.49</v>
       </c>
-      <c r="C108" s="126">
+      <c r="C108" s="114">
         <v>5000</v>
       </c>
-      <c r="D108" s="127" t="s">
+      <c r="D108" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E108" s="127" t="s">
+      <c r="E108" s="115" t="s">
         <v>838</v>
       </c>
-      <c r="F108" s="127" t="s">
+      <c r="F108" s="115" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="109" spans="1:6" s="96" customFormat="1">
-      <c r="A109" s="124">
+    <row r="109" spans="1:6" s="91" customFormat="1">
+      <c r="A109" s="112">
         <v>46017</v>
       </c>
-      <c r="B109" s="125">
+      <c r="B109" s="113">
         <v>22.28</v>
       </c>
-      <c r="C109" s="126">
+      <c r="C109" s="114">
         <v>2000</v>
       </c>
-      <c r="D109" s="127" t="s">
+      <c r="D109" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E109" s="127" t="s">
+      <c r="E109" s="115" t="s">
         <v>880</v>
       </c>
-      <c r="F109" s="127" t="s">
+      <c r="F109" s="115" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="110" spans="1:6" s="96" customFormat="1">
-      <c r="A110" s="124">
+    <row r="110" spans="1:6" s="91" customFormat="1">
+      <c r="A110" s="112">
         <v>46018</v>
       </c>
-      <c r="B110" s="125">
+      <c r="B110" s="113">
         <v>22.27</v>
       </c>
-      <c r="C110" s="126">
+      <c r="C110" s="114">
         <v>2000</v>
       </c>
-      <c r="D110" s="127" t="s">
+      <c r="D110" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E110" s="127" t="s">
+      <c r="E110" s="115" t="s">
         <v>867</v>
       </c>
-      <c r="F110" s="127" t="s">
+      <c r="F110" s="115" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="111" spans="1:6" s="96" customFormat="1">
-      <c r="A111" s="124">
+    <row r="111" spans="1:6" s="91" customFormat="1">
+      <c r="A111" s="112">
         <v>46018</v>
       </c>
-      <c r="B111" s="125">
+      <c r="B111" s="113">
         <v>556.70000000000005</v>
       </c>
-      <c r="C111" s="126">
+      <c r="C111" s="114">
         <v>50000</v>
       </c>
-      <c r="D111" s="127" t="s">
+      <c r="D111" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E111" s="127" t="s">
+      <c r="E111" s="115" t="s">
         <v>881</v>
       </c>
-      <c r="F111" s="127" t="s">
+      <c r="F111" s="115" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="112" spans="1:6" s="96" customFormat="1">
-      <c r="A112" s="124">
+    <row r="112" spans="1:6" s="91" customFormat="1">
+      <c r="A112" s="112">
         <v>46019</v>
       </c>
-      <c r="B112" s="125">
+      <c r="B112" s="113">
         <v>6.39</v>
       </c>
-      <c r="C112" s="126">
+      <c r="C112" s="114">
         <v>574</v>
       </c>
-      <c r="D112" s="127" t="s">
+      <c r="D112" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E112" s="127" t="s">
+      <c r="E112" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="F112" s="127" t="s">
+      <c r="F112" s="115" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="96" customFormat="1">
-      <c r="A113" s="124">
+    <row r="113" spans="1:10" s="91" customFormat="1">
+      <c r="A113" s="112">
         <v>46020</v>
       </c>
-      <c r="B113" s="125">
+      <c r="B113" s="113">
         <v>556.16</v>
       </c>
-      <c r="C113" s="126">
+      <c r="C113" s="114">
         <v>50000</v>
       </c>
-      <c r="D113" s="127" t="s">
+      <c r="D113" s="115" t="s">
         <v>261</v>
       </c>
-      <c r="E113" s="127" t="s">
+      <c r="E113" s="115" t="s">
         <v>881</v>
       </c>
-      <c r="F113" s="127" t="s">
+      <c r="F113" s="115" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="114" spans="1:10" s="132" customFormat="1">
-      <c r="A114" s="128">
+    <row r="114" spans="1:10" s="120" customFormat="1">
+      <c r="A114" s="116">
         <v>46034</v>
       </c>
-      <c r="B114" s="129">
+      <c r="B114" s="117">
         <v>554.75</v>
       </c>
-      <c r="C114" s="130">
+      <c r="C114" s="118">
         <v>50000</v>
       </c>
-      <c r="D114" s="131" t="s">
+      <c r="D114" s="119" t="s">
         <v>261</v>
       </c>
-      <c r="E114" s="131" t="s">
+      <c r="E114" s="119" t="s">
         <v>883</v>
       </c>
-      <c r="F114" s="131" t="s">
+      <c r="F114" s="119" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="132" customFormat="1">
-      <c r="A115" s="128">
+    <row r="115" spans="1:10" s="120" customFormat="1">
+      <c r="A115" s="116">
         <v>46055</v>
       </c>
-      <c r="B115" s="129">
+      <c r="B115" s="117">
         <v>552.94000000000005</v>
       </c>
-      <c r="C115" s="130">
+      <c r="C115" s="118">
         <v>50000</v>
       </c>
-      <c r="D115" s="131" t="s">
+      <c r="D115" s="119" t="s">
         <v>261</v>
       </c>
-      <c r="E115" s="131" t="s">
+      <c r="E115" s="119" t="s">
         <v>884</v>
       </c>
-      <c r="F115" s="131" t="s">
+      <c r="F115" s="119" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="132" customFormat="1">
-      <c r="A116" s="128">
+    <row r="116" spans="1:10" s="120" customFormat="1">
+      <c r="A116" s="116">
         <v>46070</v>
       </c>
-      <c r="B116" s="129">
+      <c r="B116" s="117">
         <v>33.1</v>
       </c>
-      <c r="C116" s="130">
+      <c r="C116" s="118">
         <v>3000</v>
       </c>
-      <c r="D116" s="131" t="s">
+      <c r="D116" s="119" t="s">
         <v>261</v>
       </c>
-      <c r="E116" s="131" t="s">
+      <c r="E116" s="119" t="s">
         <v>885</v>
       </c>
-      <c r="F116" s="131" t="s">
+      <c r="F116" s="119" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="132" customFormat="1">
-      <c r="A117" s="128"/>
-      <c r="B117" s="129">
+    <row r="117" spans="1:10" s="120" customFormat="1">
+      <c r="A117" s="116"/>
+      <c r="B117" s="117">
         <v>112.56</v>
       </c>
-      <c r="C117" s="130">
+      <c r="C117" s="118">
         <v>10000</v>
       </c>
-      <c r="D117" s="131"/>
-      <c r="E117" s="131"/>
-      <c r="F117" s="131" t="s">
+      <c r="D117" s="119"/>
+      <c r="E117" s="119"/>
+      <c r="F117" s="119" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="118" spans="1:10" s="132" customFormat="1">
-      <c r="A118" s="128"/>
-      <c r="B118" s="129">
+    <row r="118" spans="1:10" s="120" customFormat="1">
+      <c r="A118" s="116"/>
+      <c r="B118" s="117">
         <v>104.49</v>
       </c>
-      <c r="C118" s="130">
+      <c r="C118" s="118">
         <v>10000</v>
       </c>
-      <c r="D118" s="131" t="s">
+      <c r="D118" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="E118" s="131" t="s">
+      <c r="E118" s="119" t="s">
         <v>887</v>
       </c>
-      <c r="F118" s="131" t="s">
+      <c r="F118" s="119" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="71">
+      <c r="A119" s="70">
         <v>45602</v>
       </c>
-      <c r="B119" s="72">
+      <c r="B119" s="71">
         <v>5</v>
       </c>
-      <c r="C119" s="73">
+      <c r="C119" s="72">
         <v>500</v>
       </c>
-      <c r="D119" s="74" t="s">
+      <c r="D119" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="E119" s="74" t="s">
+      <c r="E119" s="73" t="s">
         <v>892</v>
       </c>
-      <c r="F119" s="74" t="s">
+      <c r="F119" s="73" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="71">
+      <c r="A120" s="70">
         <v>45369</v>
       </c>
-      <c r="B120" s="72">
+      <c r="B120" s="71">
         <v>5</v>
       </c>
-      <c r="C120" s="73">
+      <c r="C120" s="72">
         <v>500</v>
       </c>
-      <c r="D120" s="74" t="s">
+      <c r="D120" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="E120" s="74" t="s">
+      <c r="E120" s="73" t="s">
         <v>892</v>
       </c>
-      <c r="F120" s="74" t="s">
+      <c r="F120" s="73" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="71"/>
-      <c r="B121" s="72">
+      <c r="A121" s="70"/>
+      <c r="B121" s="71">
         <v>113.04</v>
       </c>
-      <c r="C121" s="73">
+      <c r="C121" s="72">
         <v>10000</v>
       </c>
-      <c r="D121" s="74"/>
-      <c r="E121" s="74" t="s">
+      <c r="D121" s="73"/>
+      <c r="E121" s="73" t="s">
         <v>251</v>
       </c>
-      <c r="F121" s="74" t="s">
+      <c r="F121" s="73" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="71"/>
-      <c r="B122" s="72"/>
-      <c r="C122" s="75"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="74" t="s">
+      <c r="A122" s="70"/>
+      <c r="B122" s="71"/>
+      <c r="C122" s="74"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="73" t="s">
         <v>889</v>
       </c>
-      <c r="F122" s="74" t="s">
+      <c r="F122" s="73" t="s">
         <v>890</v>
       </c>
     </row>
@@ -61930,24 +61905,24 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:1" s="134" customFormat="1">
-      <c r="A130" s="134" t="s">
+    <row r="130" spans="1:1" s="152" customFormat="1">
+      <c r="A130" s="152" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="131" spans="1:1" s="134" customFormat="1">
-      <c r="A131" s="134" t="s">
+    <row r="131" spans="1:1" s="152" customFormat="1">
+      <c r="A131" s="152" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="132" spans="1:1" s="133" customFormat="1">
-      <c r="A132" s="133" t="s">
+    <row r="132" spans="1:1" s="145" customFormat="1">
+      <c r="A132" s="145" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="133" spans="1:1" s="101" customFormat="1"/>
-    <row r="134" spans="1:1" s="133" customFormat="1">
-      <c r="A134" s="133" t="s">
+    <row r="133" spans="1:1" s="153" customFormat="1"/>
+    <row r="134" spans="1:1" s="145" customFormat="1">
+      <c r="A134" s="145" t="s">
         <v>999</v>
       </c>
     </row>
@@ -62399,7 +62374,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="147">
+      <c r="A23" s="131">
         <v>45894</v>
       </c>
       <c r="B23" s="2"/>
@@ -62587,7 +62562,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1">
-      <c r="A2" s="77">
+      <c r="A2" s="76">
         <v>44834</v>
       </c>
       <c r="B2" s="25" t="s">
@@ -63143,109 +63118,109 @@
         <v>493</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="78" customFormat="1">
-      <c r="A8" s="78" t="s">
+    <row r="8" spans="1:12" s="77" customFormat="1">
+      <c r="A8" s="77" t="s">
         <v>336</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="77" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="78" t="s">
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="77" t="s">
         <v>337</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="77" t="s">
         <v>338</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="77" t="s">
         <v>339</v>
       </c>
-      <c r="H8" s="80">
+      <c r="H8" s="79">
         <v>46025</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="J8" s="78" t="s">
+      <c r="J8" s="77" t="s">
         <v>320</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="77" t="s">
         <v>321</v>
       </c>
-      <c r="L8" s="78" t="s">
+      <c r="L8" s="77" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="78" customFormat="1">
-      <c r="A9" s="78" t="s">
+    <row r="9" spans="1:12" s="77" customFormat="1">
+      <c r="A9" s="77" t="s">
         <v>340</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="77" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="78">
         <v>300</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="78" t="s">
+      <c r="D9" s="78"/>
+      <c r="E9" s="77" t="s">
         <v>341</v>
       </c>
-      <c r="F9" s="78" t="s">
+      <c r="F9" s="77" t="s">
         <v>342</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="77" t="s">
         <v>339</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="79">
         <v>46008</v>
       </c>
-      <c r="I9" s="78" t="s">
+      <c r="I9" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="J9" s="78" t="s">
+      <c r="J9" s="77" t="s">
         <v>320</v>
       </c>
-      <c r="K9" s="78" t="s">
+      <c r="K9" s="77" t="s">
         <v>321</v>
       </c>
-      <c r="L9" s="78" t="s">
+      <c r="L9" s="77" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="78" customFormat="1">
-      <c r="A10" s="78" t="s">
+    <row r="10" spans="1:12" s="77" customFormat="1">
+      <c r="A10" s="77" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="77" t="s">
         <v>315</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="78">
         <v>300</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="78" t="s">
+      <c r="D10" s="78"/>
+      <c r="E10" s="77" t="s">
         <v>344</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="77" t="s">
         <v>345</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="77" t="s">
         <v>339</v>
       </c>
-      <c r="H10" s="80">
+      <c r="H10" s="79">
         <v>45871</v>
       </c>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="J10" s="78" t="s">
+      <c r="J10" s="77" t="s">
         <v>320</v>
       </c>
-      <c r="K10" s="78" t="s">
+      <c r="K10" s="77" t="s">
         <v>321</v>
       </c>
-      <c r="L10" s="78" t="s">
+      <c r="L10" s="77" t="s">
         <v>908</v>
       </c>
     </row>
@@ -65003,125 +64978,125 @@
     <col min="5" max="5" width="38.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="81" customFormat="1">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:5" s="80" customFormat="1">
+      <c r="A1" s="80" t="s">
         <v>1069</v>
       </c>
-      <c r="B1" s="143" t="s">
+      <c r="B1" s="127" t="s">
         <v>1060</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="80" t="s">
         <v>1070</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="80" t="s">
         <v>1071</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="80" t="s">
         <v>1072</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="B3" s="144">
+      <c r="B3" s="128">
         <v>45292</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="144">
+      <c r="B4" s="128">
         <v>45323</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="144">
+      <c r="B5" s="128">
         <v>45352</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6" s="144">
+      <c r="B6" s="128">
         <v>45383</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="144">
+      <c r="B7" s="128">
         <v>45413</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" s="144">
+      <c r="B8" s="128">
         <v>45444</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="144">
+      <c r="B9" s="128">
         <v>45474</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="144">
+      <c r="B10" s="128">
         <v>45505</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="B11" s="144">
+      <c r="B11" s="128">
         <v>45536</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="B12" s="144">
+      <c r="B12" s="128">
         <v>45566</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13" s="144">
+      <c r="B13" s="128">
         <v>45597</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="B14" s="144">
+      <c r="B14" s="128">
         <v>45627</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="B15" s="144">
+      <c r="B15" s="128">
         <v>45658</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="144">
+      <c r="B16" s="128">
         <v>45689</v>
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="144">
+      <c r="B17" s="128">
         <v>45717</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="144">
+      <c r="B18" s="128">
         <v>45748</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="144">
+      <c r="B19" s="128">
         <v>45778</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="144">
+      <c r="B20" s="128">
         <v>45809</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="144">
+      <c r="B21" s="128">
         <v>45839</v>
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="144">
+      <c r="B22" s="128">
         <v>45870</v>
       </c>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="144">
+      <c r="B23" s="128">
         <v>45901</v>
       </c>
     </row>
